--- a/pkcs11_tests/perf_report.xlsx
+++ b/pkcs11_tests/perf_report.xlsx
@@ -22,10 +22,10 @@
     <sheet name="Vue d'ensemble" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Résumé'!$A$3:$I$119</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Résumé'!$A$3:$I$118</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'AES'!$A$2:$I$42</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'DES3'!$A$2:$I$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'RSA'!$A$2:$I$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'RSA'!$A$2:$I$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'EC'!$A$2:$I$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'EdDSA'!$A$2:$I$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'DSA'!$A$2:$I$4</definedName>
@@ -766,12 +766,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vue d''ensemble'!$A$3:$A$47</f>
+              <f>'Vue d''ensemble'!$A$3:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vue d''ensemble'!$B$3:$B$47</f>
+              <f>'Vue d''ensemble'!$B$3:$B$46</f>
             </numRef>
           </val>
         </ser>
@@ -974,7 +974,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'RSA'!B22</f>
+              <f>'RSA'!B21</f>
             </strRef>
           </tx>
           <spPr>
@@ -984,12 +984,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'RSA'!$A$23:$A$39</f>
+              <f>'RSA'!$A$22:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'RSA'!$B$23:$B$39</f>
+              <f>'RSA'!$B$22:$B$37</f>
             </numRef>
           </val>
         </ser>
@@ -1800,7 +1800,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9360000" cy="8100000"/>
+    <ext cx="9360000" cy="7920000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1851,10 +1851,10 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>21</row>
+      <row>20</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7920000" cy="3366000"/>
+    <ext cx="7920000" cy="3168000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -2323,7 +2323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I119"/>
+  <dimension ref="A1:I118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2340,14 +2340,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Rapport de performance PKCS#11 — SoftHSM2  |  Généré le 2026-06-06 14:48</t>
+          <t>Rapport de performance PKCS#11 — SoftHSM2  |  Généré le 2026-06-06 17:50</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   116 mesures  ·  11 catégories  ·  35 mécanismes uniques</t>
+          <t xml:space="preserve">   115 mesures  ·  11 catégories  ·  35 mécanismes uniques</t>
         </is>
       </c>
     </row>
@@ -2423,13 +2423,13 @@
         </is>
       </c>
       <c r="F4" s="6" t="n">
-        <v>72979.8</v>
+        <v>10815.6</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.0137</v>
+        <v>0.0925</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>4.45</v>
+        <v>0.66</v>
       </c>
       <c r="I4" s="5" t="inlineStr"/>
     </row>
@@ -2458,13 +2458,13 @@
         </is>
       </c>
       <c r="F5" s="6" t="n">
-        <v>66503</v>
+        <v>5566.3</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.015</v>
+        <v>0.1797</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>64.94</v>
+        <v>5.44</v>
       </c>
       <c r="I5" s="5" t="inlineStr"/>
     </row>
@@ -2493,13 +2493,13 @@
         </is>
       </c>
       <c r="F6" s="6" t="n">
-        <v>9831.799999999999</v>
+        <v>167.1</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.1017</v>
+        <v>5.9847</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>614.49</v>
+        <v>10.44</v>
       </c>
       <c r="I6" s="5" t="inlineStr"/>
     </row>
@@ -2528,13 +2528,13 @@
         </is>
       </c>
       <c r="F7" s="6" t="n">
-        <v>336.1</v>
+        <v>10.3</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>2.9755</v>
+        <v>96.7383</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>336.07</v>
+        <v>10.34</v>
       </c>
       <c r="I7" s="5" t="inlineStr"/>
     </row>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="F8" s="6" t="n">
-        <v>65721.8</v>
+        <v>5396.6</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.0152</v>
+        <v>0.1853</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>64.18000000000001</v>
+        <v>5.27</v>
       </c>
       <c r="I8" s="5" t="inlineStr"/>
     </row>
@@ -2598,13 +2598,13 @@
         </is>
       </c>
       <c r="F9" s="6" t="n">
-        <v>9036.700000000001</v>
+        <v>169.7</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.1107</v>
+        <v>5.8912</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>564.79</v>
+        <v>10.61</v>
       </c>
       <c r="I9" s="5" t="inlineStr"/>
     </row>
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>73947.89999999999</v>
+        <v>11064.9</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.0135</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>4.51</v>
+        <v>0.68</v>
       </c>
       <c r="I10" s="5" t="inlineStr"/>
     </row>
@@ -2668,13 +2668,13 @@
         </is>
       </c>
       <c r="F11" s="6" t="n">
-        <v>65620.60000000001</v>
+        <v>5628</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.0152</v>
+        <v>0.1777</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>64.08</v>
+        <v>5.5</v>
       </c>
       <c r="I11" s="5" t="inlineStr"/>
     </row>
@@ -2703,13 +2703,13 @@
         </is>
       </c>
       <c r="F12" s="6" t="n">
-        <v>8414.6</v>
+        <v>168.7</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.1188</v>
+        <v>5.9264</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>525.91</v>
+        <v>10.55</v>
       </c>
       <c r="I12" s="5" t="inlineStr"/>
     </row>
@@ -2738,13 +2738,13 @@
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>307.7</v>
+        <v>10.3</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>3.2496</v>
+        <v>97.32850000000001</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>307.73</v>
+        <v>10.27</v>
       </c>
       <c r="I13" s="5" t="inlineStr"/>
     </row>
@@ -2773,13 +2773,13 @@
         </is>
       </c>
       <c r="F14" s="6" t="n">
-        <v>76377.89999999999</v>
+        <v>11150.1</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.0131</v>
+        <v>0.0897</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>4.66</v>
+        <v>0.68</v>
       </c>
       <c r="I14" s="5" t="inlineStr"/>
     </row>
@@ -2808,13 +2808,13 @@
         </is>
       </c>
       <c r="F15" s="6" t="n">
-        <v>67089.10000000001</v>
+        <v>5031.1</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.0149</v>
+        <v>0.1988</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>65.52</v>
+        <v>4.91</v>
       </c>
       <c r="I15" s="5" t="inlineStr"/>
     </row>
@@ -2843,13 +2843,13 @@
         </is>
       </c>
       <c r="F16" s="6" t="n">
-        <v>10771.7</v>
+        <v>143.1</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.09279999999999999</v>
+        <v>6.9874</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>673.23</v>
+        <v>8.94</v>
       </c>
       <c r="I16" s="5" t="inlineStr"/>
     </row>
@@ -2878,13 +2878,13 @@
         </is>
       </c>
       <c r="F17" s="6" t="n">
-        <v>374</v>
+        <v>8.6</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>2.6739</v>
+        <v>116.3753</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>373.99</v>
+        <v>8.59</v>
       </c>
       <c r="I17" s="5" t="inlineStr"/>
     </row>
@@ -2913,13 +2913,13 @@
         </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>76018.8</v>
+        <v>10438</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.0132</v>
+        <v>0.0958</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>4.64</v>
+        <v>0.64</v>
       </c>
       <c r="I18" s="5" t="inlineStr"/>
     </row>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="F19" s="6" t="n">
-        <v>64676.3</v>
+        <v>4876.7</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.0155</v>
+        <v>0.2051</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>63.16</v>
+        <v>4.76</v>
       </c>
       <c r="I19" s="5" t="inlineStr"/>
     </row>
@@ -2983,13 +2983,13 @@
         </is>
       </c>
       <c r="F20" s="6" t="n">
-        <v>10895.3</v>
+        <v>140.3</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.09180000000000001</v>
+        <v>7.1273</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>680.96</v>
+        <v>8.77</v>
       </c>
       <c r="I20" s="5" t="inlineStr"/>
     </row>
@@ -3018,13 +3018,13 @@
         </is>
       </c>
       <c r="F21" s="6" t="n">
-        <v>371.5</v>
+        <v>8.6</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>2.6921</v>
+        <v>115.7334</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>371.45</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="I21" s="5" t="inlineStr"/>
     </row>
@@ -3053,13 +3053,13 @@
         </is>
       </c>
       <c r="F22" s="6" t="n">
-        <v>76104.60000000001</v>
+        <v>12372.7</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.0131</v>
+        <v>0.0808</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>4.65</v>
+        <v>0.76</v>
       </c>
       <c r="I22" s="5" t="inlineStr"/>
     </row>
@@ -3088,13 +3088,13 @@
         </is>
       </c>
       <c r="F23" s="6" t="n">
-        <v>70636.7</v>
+        <v>7976.9</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.0142</v>
+        <v>0.1254</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>68.98</v>
+        <v>7.79</v>
       </c>
       <c r="I23" s="5" t="inlineStr"/>
     </row>
@@ -3123,13 +3123,13 @@
         </is>
       </c>
       <c r="F24" s="6" t="n">
-        <v>13498.8</v>
+        <v>331.5</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.0741</v>
+        <v>3.0168</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>843.67</v>
+        <v>20.72</v>
       </c>
       <c r="I24" s="5" t="inlineStr"/>
     </row>
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="F25" s="6" t="n">
-        <v>75945.60000000001</v>
+        <v>11979.3</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.0132</v>
+        <v>0.0835</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>4.64</v>
+        <v>0.73</v>
       </c>
       <c r="I25" s="5" t="inlineStr"/>
     </row>
@@ -3193,13 +3193,13 @@
         </is>
       </c>
       <c r="F26" s="6" t="n">
-        <v>69146.10000000001</v>
+        <v>7884.1</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.0145</v>
+        <v>0.1268</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>67.53</v>
+        <v>7.7</v>
       </c>
       <c r="I26" s="5" t="inlineStr"/>
     </row>
@@ -3228,13 +3228,13 @@
         </is>
       </c>
       <c r="F27" s="6" t="n">
-        <v>10655.9</v>
+        <v>329</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.09379999999999999</v>
+        <v>3.0396</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>666</v>
+        <v>20.56</v>
       </c>
       <c r="I27" s="5" t="inlineStr"/>
     </row>
@@ -3263,13 +3263,13 @@
         </is>
       </c>
       <c r="F28" s="6" t="n">
-        <v>62435.2</v>
+        <v>10358.4</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.016</v>
+        <v>0.0965</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>3.81</v>
+        <v>0.63</v>
       </c>
       <c r="I28" s="5" t="inlineStr"/>
     </row>
@@ -3298,13 +3298,13 @@
         </is>
       </c>
       <c r="F29" s="6" t="n">
-        <v>58775.8</v>
+        <v>5526.6</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.017</v>
+        <v>0.1809</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>57.4</v>
+        <v>5.4</v>
       </c>
       <c r="I29" s="5" t="inlineStr"/>
     </row>
@@ -3333,13 +3333,13 @@
         </is>
       </c>
       <c r="F30" s="6" t="n">
-        <v>16576.5</v>
+        <v>172.9</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.0603</v>
+        <v>5.7824</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>1036.03</v>
+        <v>10.81</v>
       </c>
       <c r="I30" s="5" t="inlineStr"/>
     </row>
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="F31" s="6" t="n">
-        <v>430.4</v>
+        <v>10.5</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>2.3235</v>
+        <v>95.0163</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>430.38</v>
+        <v>10.52</v>
       </c>
       <c r="I31" s="5" t="inlineStr"/>
     </row>
@@ -3403,13 +3403,13 @@
         </is>
       </c>
       <c r="F32" s="6" t="n">
-        <v>57906.1</v>
+        <v>10230</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.0173</v>
+        <v>0.0978</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>3.53</v>
+        <v>0.62</v>
       </c>
       <c r="I32" s="5" t="inlineStr"/>
     </row>
@@ -3438,13 +3438,13 @@
         </is>
       </c>
       <c r="F33" s="6" t="n">
-        <v>59373.9</v>
+        <v>5427.1</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0.0168</v>
+        <v>0.1843</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>57.98</v>
+        <v>5.3</v>
       </c>
       <c r="I33" s="5" t="inlineStr"/>
     </row>
@@ -3473,13 +3473,13 @@
         </is>
       </c>
       <c r="F34" s="6" t="n">
-        <v>15144</v>
+        <v>169.4</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.066</v>
+        <v>5.9016</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>946.5</v>
+        <v>10.59</v>
       </c>
       <c r="I34" s="5" t="inlineStr"/>
     </row>
@@ -3508,13 +3508,13 @@
         </is>
       </c>
       <c r="F35" s="6" t="n">
-        <v>434.9</v>
+        <v>10.5</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>2.2992</v>
+        <v>95.25839999999999</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>434.94</v>
+        <v>10.5</v>
       </c>
       <c r="I35" s="5" t="inlineStr"/>
     </row>
@@ -3543,13 +3543,13 @@
         </is>
       </c>
       <c r="F36" s="6" t="n">
-        <v>60906.3</v>
+        <v>4425.7</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>0.0164</v>
+        <v>0.226</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>59.48</v>
+        <v>4.32</v>
       </c>
       <c r="I36" s="5" t="inlineStr"/>
     </row>
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="F37" s="6" t="n">
-        <v>10797.1</v>
+        <v>117.8</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>0.0926</v>
+        <v>8.4878</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>674.8200000000001</v>
+        <v>7.36</v>
       </c>
       <c r="I37" s="5" t="inlineStr"/>
     </row>
@@ -3613,13 +3613,13 @@
         </is>
       </c>
       <c r="F38" s="6" t="n">
-        <v>61497.1</v>
+        <v>4407</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>0.0163</v>
+        <v>0.2269</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>60.06</v>
+        <v>4.3</v>
       </c>
       <c r="I38" s="5" t="inlineStr"/>
     </row>
@@ -3648,13 +3648,13 @@
         </is>
       </c>
       <c r="F39" s="6" t="n">
-        <v>11004.5</v>
+        <v>119.2</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>0.09089999999999999</v>
+        <v>8.3901</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>687.78</v>
+        <v>7.45</v>
       </c>
       <c r="I39" s="5" t="inlineStr"/>
     </row>
@@ -3683,13 +3683,13 @@
         </is>
       </c>
       <c r="F40" s="6" t="n">
-        <v>61154</v>
+        <v>7604</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>0.0164</v>
+        <v>0.1315</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>59.72</v>
+        <v>7.43</v>
       </c>
       <c r="I40" s="5" t="inlineStr"/>
     </row>
@@ -3718,13 +3718,13 @@
         </is>
       </c>
       <c r="F41" s="6" t="n">
-        <v>27449.5</v>
+        <v>325.3</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>0.0364</v>
+        <v>3.0743</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>1715.59</v>
+        <v>20.33</v>
       </c>
       <c r="I41" s="5" t="inlineStr"/>
     </row>
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="F42" s="6" t="n">
-        <v>59056.1</v>
+        <v>7250.8</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>0.0169</v>
+        <v>0.1379</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>57.67</v>
+        <v>7.08</v>
       </c>
       <c r="I42" s="5" t="inlineStr"/>
     </row>
@@ -3788,13 +3788,13 @@
         </is>
       </c>
       <c r="F43" s="6" t="n">
-        <v>25435.2</v>
+        <v>327.9</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>0.0393</v>
+        <v>3.0497</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>1589.7</v>
+        <v>20.49</v>
       </c>
       <c r="I43" s="5" t="inlineStr"/>
     </row>
@@ -3823,13 +3823,13 @@
         </is>
       </c>
       <c r="F44" s="9" t="n">
-        <v>61158.9</v>
+        <v>11192.5</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>0.0164</v>
+        <v>0.0893</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>3.73</v>
+        <v>0.68</v>
       </c>
       <c r="I44" s="8" t="inlineStr"/>
     </row>
@@ -3858,13 +3858,13 @@
         </is>
       </c>
       <c r="F45" s="9" t="n">
-        <v>17658.7</v>
+        <v>4434</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>0.0566</v>
+        <v>0.2255</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>17.24</v>
+        <v>4.33</v>
       </c>
       <c r="I45" s="8" t="inlineStr"/>
     </row>
@@ -3893,13 +3893,13 @@
         </is>
       </c>
       <c r="F46" s="9" t="n">
-        <v>360.5</v>
+        <v>120.9</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>2.7736</v>
+        <v>8.2723</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>22.53</v>
+        <v>7.56</v>
       </c>
       <c r="I46" s="8" t="inlineStr"/>
     </row>
@@ -3928,13 +3928,13 @@
         </is>
       </c>
       <c r="F47" s="9" t="n">
-        <v>60446.2</v>
+        <v>11805.6</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>0.0165</v>
+        <v>0.0847</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>3.69</v>
+        <v>0.72</v>
       </c>
       <c r="I47" s="8" t="inlineStr"/>
     </row>
@@ -3963,13 +3963,13 @@
         </is>
       </c>
       <c r="F48" s="9" t="n">
-        <v>18328.2</v>
+        <v>6086.7</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>0.0546</v>
+        <v>0.1643</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>17.9</v>
+        <v>5.94</v>
       </c>
       <c r="I48" s="8" t="inlineStr"/>
     </row>
@@ -3998,13 +3998,13 @@
         </is>
       </c>
       <c r="F49" s="9" t="n">
-        <v>393.1</v>
+        <v>185.4</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>2.5439</v>
+        <v>5.395</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>24.57</v>
+        <v>11.58</v>
       </c>
       <c r="I49" s="8" t="inlineStr"/>
     </row>
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="F50" s="12" t="n">
-        <v>3425.7</v>
+        <v>1320.8</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.2919</v>
+        <v>0.7571</v>
       </c>
       <c r="H50" s="12" t="inlineStr">
         <is>
@@ -4070,10 +4070,10 @@
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>1270.3</v>
+        <v>578</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.7872</v>
+        <v>1.7301</v>
       </c>
       <c r="H51" s="12" t="inlineStr">
         <is>
@@ -4107,10 +4107,10 @@
         </is>
       </c>
       <c r="F52" s="12" t="n">
-        <v>576.9</v>
+        <v>282</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>1.7333</v>
+        <v>3.5456</v>
       </c>
       <c r="H52" s="12" t="inlineStr">
         <is>
@@ -4144,10 +4144,10 @@
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>297.5</v>
+        <v>152.8</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>3.3611</v>
+        <v>6.5466</v>
       </c>
       <c r="H53" s="12" t="inlineStr">
         <is>
@@ -4181,10 +4181,10 @@
         </is>
       </c>
       <c r="F54" s="12" t="n">
-        <v>46211.3</v>
+        <v>8377</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.0216</v>
+        <v>0.1194</v>
       </c>
       <c r="H54" s="12" t="inlineStr">
         <is>
@@ -4218,10 +4218,10 @@
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>25380.5</v>
+        <v>7262.4</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.0394</v>
+        <v>0.1377</v>
       </c>
       <c r="H55" s="12" t="inlineStr">
         <is>
@@ -4255,10 +4255,10 @@
         </is>
       </c>
       <c r="F56" s="12" t="n">
-        <v>15042.3</v>
+        <v>5040.9</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.0665</v>
+        <v>0.1984</v>
       </c>
       <c r="H56" s="12" t="inlineStr">
         <is>
@@ -4292,10 +4292,10 @@
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>9720.9</v>
+        <v>4228.7</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.1029</v>
+        <v>0.2365</v>
       </c>
       <c r="H57" s="12" t="inlineStr">
         <is>
@@ -4329,13 +4329,13 @@
         </is>
       </c>
       <c r="F58" s="12" t="n">
-        <v>26587.2</v>
+        <v>8962.4</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.0376</v>
+        <v>0.1116</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>1.62</v>
+        <v>0.55</v>
       </c>
       <c r="I58" s="11" t="inlineStr"/>
     </row>
@@ -4364,13 +4364,13 @@
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>1205.2</v>
+        <v>583.4</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.8297</v>
+        <v>1.714</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="I59" s="11" t="inlineStr"/>
     </row>
@@ -4399,10 +4399,10 @@
         </is>
       </c>
       <c r="F60" s="12" t="n">
-        <v>1223.9</v>
+        <v>587.3</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.8169999999999999</v>
+        <v>1.7028</v>
       </c>
       <c r="H60" s="12" t="inlineStr">
         <is>
@@ -4436,10 +4436,10 @@
         </is>
       </c>
       <c r="F61" s="12" t="n">
-        <v>1151.5</v>
+        <v>571.2</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.8683999999999999</v>
+        <v>1.7506</v>
       </c>
       <c r="H61" s="12" t="inlineStr">
         <is>
@@ -4473,10 +4473,10 @@
         </is>
       </c>
       <c r="F62" s="12" t="n">
-        <v>1233</v>
+        <v>575.3</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.8110000000000001</v>
+        <v>1.7382</v>
       </c>
       <c r="H62" s="12" t="inlineStr">
         <is>
@@ -4510,10 +4510,10 @@
         </is>
       </c>
       <c r="F63" s="12" t="n">
-        <v>19851.1</v>
+        <v>6707.5</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.0504</v>
+        <v>0.1491</v>
       </c>
       <c r="H63" s="12" t="inlineStr">
         <is>
@@ -4547,10 +4547,10 @@
         </is>
       </c>
       <c r="F64" s="12" t="n">
-        <v>22922.8</v>
+        <v>6605.3</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.0436</v>
+        <v>0.1514</v>
       </c>
       <c r="H64" s="12" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>encrypt</t>
+          <t>decrypt</t>
         </is>
       </c>
       <c r="D65" s="11" t="n">
@@ -4584,53 +4584,55 @@
         </is>
       </c>
       <c r="F65" s="12" t="n">
-        <v>25554</v>
+        <v>587</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.0391</v>
+        <v>1.7037</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>6.24</v>
+        <v>0.14</v>
       </c>
       <c r="I65" s="11" t="inlineStr"/>
     </row>
     <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="11" t="inlineStr">
-        <is>
-          <t>RSA</t>
-        </is>
-      </c>
-      <c r="B66" s="11" t="inlineStr">
-        <is>
-          <t>RSA_X_509</t>
-        </is>
-      </c>
-      <c r="C66" s="11" t="inlineStr">
-        <is>
-          <t>decrypt</t>
-        </is>
-      </c>
-      <c r="D66" s="11" t="n">
-        <v>2048</v>
-      </c>
-      <c r="E66" s="11" t="inlineStr">
-        <is>
-          <t>256 B</t>
-        </is>
-      </c>
-      <c r="F66" s="12" t="n">
-        <v>1196.6</v>
-      </c>
-      <c r="G66" s="12" t="n">
-        <v>0.8357</v>
-      </c>
-      <c r="H66" s="12" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="I66" s="11" t="inlineStr"/>
+      <c r="A66" s="13" t="inlineStr">
+        <is>
+          <t>EC</t>
+        </is>
+      </c>
+      <c r="B66" s="14" t="inlineStr">
+        <is>
+          <t>ECDSA</t>
+        </is>
+      </c>
+      <c r="C66" s="14" t="inlineStr">
+        <is>
+          <t>sign</t>
+        </is>
+      </c>
+      <c r="D66" s="14" t="n">
+        <v>256</v>
+      </c>
+      <c r="E66" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F66" s="15" t="n">
+        <v>5524</v>
+      </c>
+      <c r="G66" s="15" t="n">
+        <v>0.181</v>
+      </c>
+      <c r="H66" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I66" s="14" t="inlineStr"/>
     </row>
     <row r="67" ht="16" customHeight="1">
-      <c r="A67" s="13" t="inlineStr">
+      <c r="A67" s="14" t="inlineStr">
         <is>
           <t>EC</t>
         </is>
@@ -4646,7 +4648,7 @@
         </is>
       </c>
       <c r="D67" s="14" t="n">
-        <v>256</v>
+        <v>384</v>
       </c>
       <c r="E67" s="14" t="inlineStr">
         <is>
@@ -4654,10 +4656,10 @@
         </is>
       </c>
       <c r="F67" s="15" t="n">
-        <v>15954</v>
+        <v>810.6</v>
       </c>
       <c r="G67" s="15" t="n">
-        <v>0.06270000000000001</v>
+        <v>1.2336</v>
       </c>
       <c r="H67" s="15" t="inlineStr">
         <is>
@@ -4683,7 +4685,7 @@
         </is>
       </c>
       <c r="D68" s="14" t="n">
-        <v>384</v>
+        <v>521</v>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
@@ -4691,10 +4693,10 @@
         </is>
       </c>
       <c r="F68" s="15" t="n">
-        <v>1173.4</v>
+        <v>1820.3</v>
       </c>
       <c r="G68" s="15" t="n">
-        <v>0.8522</v>
+        <v>0.5494</v>
       </c>
       <c r="H68" s="15" t="inlineStr">
         <is>
@@ -4716,11 +4718,11 @@
       </c>
       <c r="C69" s="14" t="inlineStr">
         <is>
-          <t>sign</t>
+          <t>verify</t>
         </is>
       </c>
       <c r="D69" s="14" t="n">
-        <v>521</v>
+        <v>256</v>
       </c>
       <c r="E69" s="14" t="inlineStr">
         <is>
@@ -4728,10 +4730,10 @@
         </is>
       </c>
       <c r="F69" s="15" t="n">
-        <v>3073.8</v>
+        <v>5522.2</v>
       </c>
       <c r="G69" s="15" t="n">
-        <v>0.3253</v>
+        <v>0.1811</v>
       </c>
       <c r="H69" s="15" t="inlineStr">
         <is>
@@ -4757,7 +4759,7 @@
         </is>
       </c>
       <c r="D70" s="14" t="n">
-        <v>256</v>
+        <v>384</v>
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
@@ -4765,10 +4767,10 @@
         </is>
       </c>
       <c r="F70" s="15" t="n">
-        <v>9280.299999999999</v>
+        <v>980.1</v>
       </c>
       <c r="G70" s="15" t="n">
-        <v>0.1078</v>
+        <v>1.0203</v>
       </c>
       <c r="H70" s="15" t="inlineStr">
         <is>
@@ -4794,7 +4796,7 @@
         </is>
       </c>
       <c r="D71" s="14" t="n">
-        <v>384</v>
+        <v>521</v>
       </c>
       <c r="E71" s="14" t="inlineStr">
         <is>
@@ -4802,10 +4804,10 @@
         </is>
       </c>
       <c r="F71" s="15" t="n">
-        <v>1381.1</v>
+        <v>1295.9</v>
       </c>
       <c r="G71" s="15" t="n">
-        <v>0.7241</v>
+        <v>0.7716</v>
       </c>
       <c r="H71" s="15" t="inlineStr">
         <is>
@@ -4822,16 +4824,16 @@
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>ECDSA</t>
+          <t>ECDH1_DERIVE</t>
         </is>
       </c>
       <c r="C72" s="14" t="inlineStr">
         <is>
-          <t>verify</t>
+          <t>derive</t>
         </is>
       </c>
       <c r="D72" s="14" t="n">
-        <v>521</v>
+        <v>256</v>
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
@@ -4839,10 +4841,10 @@
         </is>
       </c>
       <c r="F72" s="15" t="n">
-        <v>1705.7</v>
+        <v>1228.9</v>
       </c>
       <c r="G72" s="15" t="n">
-        <v>0.5863</v>
+        <v>0.8137</v>
       </c>
       <c r="H72" s="15" t="inlineStr">
         <is>
@@ -4868,7 +4870,7 @@
         </is>
       </c>
       <c r="D73" s="14" t="n">
-        <v>256</v>
+        <v>384</v>
       </c>
       <c r="E73" s="14" t="inlineStr">
         <is>
@@ -4876,10 +4878,10 @@
         </is>
       </c>
       <c r="F73" s="15" t="n">
-        <v>4148.2</v>
+        <v>568.8</v>
       </c>
       <c r="G73" s="15" t="n">
-        <v>0.2411</v>
+        <v>1.7582</v>
       </c>
       <c r="H73" s="15" t="inlineStr">
         <is>
@@ -4905,7 +4907,7 @@
         </is>
       </c>
       <c r="D74" s="14" t="n">
-        <v>384</v>
+        <v>521</v>
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
@@ -4913,10 +4915,10 @@
         </is>
       </c>
       <c r="F74" s="15" t="n">
-        <v>1063.6</v>
+        <v>812.2</v>
       </c>
       <c r="G74" s="15" t="n">
-        <v>0.9402</v>
+        <v>1.2312</v>
       </c>
       <c r="H74" s="15" t="inlineStr">
         <is>
@@ -4926,44 +4928,42 @@
       <c r="I74" s="14" t="inlineStr"/>
     </row>
     <row r="75" ht="16" customHeight="1">
-      <c r="A75" s="14" t="inlineStr">
-        <is>
-          <t>EC</t>
-        </is>
-      </c>
-      <c r="B75" s="14" t="inlineStr">
-        <is>
-          <t>ECDH1_DERIVE</t>
-        </is>
-      </c>
-      <c r="C75" s="14" t="inlineStr">
-        <is>
-          <t>derive</t>
-        </is>
-      </c>
-      <c r="D75" s="14" t="n">
-        <v>521</v>
-      </c>
-      <c r="E75" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F75" s="15" t="n">
-        <v>1886.5</v>
-      </c>
-      <c r="G75" s="15" t="n">
-        <v>0.5301</v>
-      </c>
-      <c r="H75" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I75" s="14" t="inlineStr"/>
+      <c r="A75" s="16" t="inlineStr">
+        <is>
+          <t>EdDSA</t>
+        </is>
+      </c>
+      <c r="B75" s="17" t="inlineStr">
+        <is>
+          <t>EDDSA</t>
+        </is>
+      </c>
+      <c r="C75" s="17" t="inlineStr">
+        <is>
+          <t>sign</t>
+        </is>
+      </c>
+      <c r="D75" s="17" t="n">
+        <v>256</v>
+      </c>
+      <c r="E75" s="17" t="inlineStr">
+        <is>
+          <t>64 B</t>
+        </is>
+      </c>
+      <c r="F75" s="18" t="n">
+        <v>2555.7</v>
+      </c>
+      <c r="G75" s="18" t="n">
+        <v>0.3913</v>
+      </c>
+      <c r="H75" s="18" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="I75" s="17" t="inlineStr"/>
     </row>
     <row r="76" ht="16" customHeight="1">
-      <c r="A76" s="16" t="inlineStr">
+      <c r="A76" s="17" t="inlineStr">
         <is>
           <t>EdDSA</t>
         </is>
@@ -4983,17 +4983,17 @@
       </c>
       <c r="E76" s="17" t="inlineStr">
         <is>
-          <t>64 B</t>
+          <t>1 KB</t>
         </is>
       </c>
       <c r="F76" s="18" t="n">
-        <v>4347.3</v>
+        <v>2361.4</v>
       </c>
       <c r="G76" s="18" t="n">
-        <v>0.23</v>
+        <v>0.4235</v>
       </c>
       <c r="H76" s="18" t="n">
-        <v>0.27</v>
+        <v>2.31</v>
       </c>
       <c r="I76" s="17" t="inlineStr"/>
     </row>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="C77" s="17" t="inlineStr">
         <is>
-          <t>sign</t>
+          <t>verify</t>
         </is>
       </c>
       <c r="D77" s="17" t="n">
@@ -5018,17 +5018,17 @@
       </c>
       <c r="E77" s="17" t="inlineStr">
         <is>
-          <t>1 KB</t>
+          <t>64 B</t>
         </is>
       </c>
       <c r="F77" s="18" t="n">
-        <v>4940.8</v>
+        <v>2933.2</v>
       </c>
       <c r="G77" s="18" t="n">
-        <v>0.2024</v>
+        <v>0.3409</v>
       </c>
       <c r="H77" s="18" t="n">
-        <v>4.83</v>
+        <v>0.18</v>
       </c>
       <c r="I77" s="17" t="inlineStr"/>
     </row>
@@ -5053,69 +5053,71 @@
       </c>
       <c r="E78" s="17" t="inlineStr">
         <is>
-          <t>64 B</t>
+          <t>1 KB</t>
         </is>
       </c>
       <c r="F78" s="18" t="n">
-        <v>4493.7</v>
+        <v>2586.7</v>
       </c>
       <c r="G78" s="18" t="n">
-        <v>0.2225</v>
+        <v>0.3866</v>
       </c>
       <c r="H78" s="18" t="n">
-        <v>0.27</v>
+        <v>2.53</v>
       </c>
       <c r="I78" s="17" t="inlineStr"/>
     </row>
     <row r="79" ht="16" customHeight="1">
-      <c r="A79" s="17" t="inlineStr">
-        <is>
-          <t>EdDSA</t>
-        </is>
-      </c>
-      <c r="B79" s="17" t="inlineStr">
-        <is>
-          <t>EDDSA</t>
-        </is>
-      </c>
-      <c r="C79" s="17" t="inlineStr">
+      <c r="A79" s="19" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+      <c r="B79" s="20" t="inlineStr">
+        <is>
+          <t>DSA_SHA256</t>
+        </is>
+      </c>
+      <c r="C79" s="20" t="inlineStr">
+        <is>
+          <t>sign</t>
+        </is>
+      </c>
+      <c r="D79" s="20" t="n">
+        <v>1024</v>
+      </c>
+      <c r="E79" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="21" t="n">
+        <v>2340</v>
+      </c>
+      <c r="G79" s="21" t="n">
+        <v>0.4274</v>
+      </c>
+      <c r="H79" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I79" s="20" t="inlineStr"/>
+    </row>
+    <row r="80" ht="16" customHeight="1">
+      <c r="A80" s="20" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+      <c r="B80" s="20" t="inlineStr">
+        <is>
+          <t>DSA_SHA256</t>
+        </is>
+      </c>
+      <c r="C80" s="20" t="inlineStr">
         <is>
           <t>verify</t>
-        </is>
-      </c>
-      <c r="D79" s="17" t="n">
-        <v>256</v>
-      </c>
-      <c r="E79" s="17" t="inlineStr">
-        <is>
-          <t>1 KB</t>
-        </is>
-      </c>
-      <c r="F79" s="18" t="n">
-        <v>4622.1</v>
-      </c>
-      <c r="G79" s="18" t="n">
-        <v>0.2164</v>
-      </c>
-      <c r="H79" s="18" t="n">
-        <v>4.51</v>
-      </c>
-      <c r="I79" s="17" t="inlineStr"/>
-    </row>
-    <row r="80" ht="16" customHeight="1">
-      <c r="A80" s="19" t="inlineStr">
-        <is>
-          <t>DSA</t>
-        </is>
-      </c>
-      <c r="B80" s="20" t="inlineStr">
-        <is>
-          <t>DSA_SHA256</t>
-        </is>
-      </c>
-      <c r="C80" s="20" t="inlineStr">
-        <is>
-          <t>sign</t>
         </is>
       </c>
       <c r="D80" s="20" t="n">
@@ -5127,10 +5129,10 @@
         </is>
       </c>
       <c r="F80" s="21" t="n">
-        <v>4703.5</v>
+        <v>4712.6</v>
       </c>
       <c r="G80" s="21" t="n">
-        <v>0.2126</v>
+        <v>0.2122</v>
       </c>
       <c r="H80" s="21" t="inlineStr">
         <is>
@@ -5140,81 +5142,79 @@
       <c r="I80" s="20" t="inlineStr"/>
     </row>
     <row r="81" ht="16" customHeight="1">
-      <c r="A81" s="20" t="inlineStr">
-        <is>
-          <t>DSA</t>
-        </is>
-      </c>
-      <c r="B81" s="20" t="inlineStr">
-        <is>
-          <t>DSA_SHA256</t>
-        </is>
-      </c>
-      <c r="C81" s="20" t="inlineStr">
-        <is>
-          <t>verify</t>
-        </is>
-      </c>
-      <c r="D81" s="20" t="n">
+      <c r="A81" s="22" t="inlineStr">
+        <is>
+          <t>DH</t>
+        </is>
+      </c>
+      <c r="B81" s="23" t="inlineStr">
+        <is>
+          <t>DH_PKCS_DERIVE</t>
+        </is>
+      </c>
+      <c r="C81" s="23" t="inlineStr">
+        <is>
+          <t>derive</t>
+        </is>
+      </c>
+      <c r="D81" s="23" t="n">
         <v>1024</v>
       </c>
-      <c r="E81" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="21" t="n">
-        <v>10344</v>
-      </c>
-      <c r="G81" s="21" t="n">
-        <v>0.09669999999999999</v>
-      </c>
-      <c r="H81" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I81" s="20" t="inlineStr"/>
+      <c r="E81" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="24" t="n">
+        <v>1174.8</v>
+      </c>
+      <c r="G81" s="24" t="n">
+        <v>0.8512</v>
+      </c>
+      <c r="H81" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="23" t="inlineStr"/>
     </row>
     <row r="82" ht="16" customHeight="1">
-      <c r="A82" s="22" t="inlineStr">
-        <is>
-          <t>DH</t>
-        </is>
-      </c>
-      <c r="B82" s="23" t="inlineStr">
-        <is>
-          <t>DH_PKCS_DERIVE</t>
-        </is>
-      </c>
-      <c r="C82" s="23" t="inlineStr">
-        <is>
-          <t>derive</t>
-        </is>
-      </c>
-      <c r="D82" s="23" t="n">
-        <v>1024</v>
-      </c>
-      <c r="E82" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F82" s="24" t="n">
-        <v>4364.6</v>
-      </c>
-      <c r="G82" s="24" t="n">
-        <v>0.2291</v>
-      </c>
-      <c r="H82" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I82" s="23" t="inlineStr"/>
+      <c r="A82" s="25" t="inlineStr">
+        <is>
+          <t>HMAC</t>
+        </is>
+      </c>
+      <c r="B82" s="26" t="inlineStr">
+        <is>
+          <t>HMAC_SHA1</t>
+        </is>
+      </c>
+      <c r="C82" s="26" t="inlineStr">
+        <is>
+          <t>sign</t>
+        </is>
+      </c>
+      <c r="D82" s="26" t="n">
+        <v>160</v>
+      </c>
+      <c r="E82" s="26" t="inlineStr">
+        <is>
+          <t>64 B</t>
+        </is>
+      </c>
+      <c r="F82" s="27" t="n">
+        <v>9570</v>
+      </c>
+      <c r="G82" s="27" t="n">
+        <v>0.1045</v>
+      </c>
+      <c r="H82" s="27" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="I82" s="26" t="inlineStr"/>
     </row>
     <row r="83" ht="16" customHeight="1">
-      <c r="A83" s="25" t="inlineStr">
+      <c r="A83" s="26" t="inlineStr">
         <is>
           <t>HMAC</t>
         </is>
@@ -5234,17 +5234,17 @@
       </c>
       <c r="E83" s="26" t="inlineStr">
         <is>
-          <t>64 B</t>
+          <t>1 KB</t>
         </is>
       </c>
       <c r="F83" s="27" t="n">
-        <v>62986.4</v>
+        <v>5641.3</v>
       </c>
       <c r="G83" s="27" t="n">
-        <v>0.0159</v>
+        <v>0.1773</v>
       </c>
       <c r="H83" s="27" t="n">
-        <v>3.84</v>
+        <v>5.51</v>
       </c>
       <c r="I83" s="26" t="inlineStr"/>
     </row>
@@ -5269,17 +5269,17 @@
       </c>
       <c r="E84" s="26" t="inlineStr">
         <is>
-          <t>1 KB</t>
+          <t>64 KB</t>
         </is>
       </c>
       <c r="F84" s="27" t="n">
-        <v>67043.8</v>
+        <v>591.4</v>
       </c>
       <c r="G84" s="27" t="n">
-        <v>0.0149</v>
+        <v>1.6908</v>
       </c>
       <c r="H84" s="27" t="n">
-        <v>65.47</v>
+        <v>36.96</v>
       </c>
       <c r="I84" s="26" t="inlineStr"/>
     </row>
@@ -5291,7 +5291,7 @@
       </c>
       <c r="B85" s="26" t="inlineStr">
         <is>
-          <t>HMAC_SHA1</t>
+          <t>HMAC_SHA256</t>
         </is>
       </c>
       <c r="C85" s="26" t="inlineStr">
@@ -5300,21 +5300,21 @@
         </is>
       </c>
       <c r="D85" s="26" t="n">
-        <v>160</v>
+        <v>256</v>
       </c>
       <c r="E85" s="26" t="inlineStr">
         <is>
-          <t>64 KB</t>
+          <t>64 B</t>
         </is>
       </c>
       <c r="F85" s="27" t="n">
-        <v>15148.2</v>
+        <v>12473.1</v>
       </c>
       <c r="G85" s="27" t="n">
-        <v>0.066</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="H85" s="27" t="n">
-        <v>946.76</v>
+        <v>0.76</v>
       </c>
       <c r="I85" s="26" t="inlineStr"/>
     </row>
@@ -5339,17 +5339,17 @@
       </c>
       <c r="E86" s="26" t="inlineStr">
         <is>
-          <t>64 B</t>
+          <t>1 KB</t>
         </is>
       </c>
       <c r="F86" s="27" t="n">
-        <v>70750.7</v>
+        <v>9561.6</v>
       </c>
       <c r="G86" s="27" t="n">
-        <v>0.0141</v>
+        <v>0.1046</v>
       </c>
       <c r="H86" s="27" t="n">
-        <v>4.32</v>
+        <v>9.34</v>
       </c>
       <c r="I86" s="26" t="inlineStr"/>
     </row>
@@ -5374,17 +5374,17 @@
       </c>
       <c r="E87" s="26" t="inlineStr">
         <is>
-          <t>1 KB</t>
+          <t>64 KB</t>
         </is>
       </c>
       <c r="F87" s="27" t="n">
-        <v>60716.5</v>
+        <v>574.6</v>
       </c>
       <c r="G87" s="27" t="n">
-        <v>0.0165</v>
+        <v>1.7403</v>
       </c>
       <c r="H87" s="27" t="n">
-        <v>59.29</v>
+        <v>35.91</v>
       </c>
       <c r="I87" s="26" t="inlineStr"/>
     </row>
@@ -5409,17 +5409,17 @@
       </c>
       <c r="E88" s="26" t="inlineStr">
         <is>
-          <t>64 KB</t>
+          <t>1 MB</t>
         </is>
       </c>
       <c r="F88" s="27" t="n">
-        <v>14234.6</v>
+        <v>37.9</v>
       </c>
       <c r="G88" s="27" t="n">
-        <v>0.0703</v>
+        <v>26.409</v>
       </c>
       <c r="H88" s="27" t="n">
-        <v>889.66</v>
+        <v>37.87</v>
       </c>
       <c r="I88" s="26" t="inlineStr"/>
     </row>
@@ -5431,7 +5431,7 @@
       </c>
       <c r="B89" s="26" t="inlineStr">
         <is>
-          <t>HMAC_SHA256</t>
+          <t>HMAC_SHA384</t>
         </is>
       </c>
       <c r="C89" s="26" t="inlineStr">
@@ -5440,21 +5440,21 @@
         </is>
       </c>
       <c r="D89" s="26" t="n">
-        <v>256</v>
+        <v>384</v>
       </c>
       <c r="E89" s="26" t="inlineStr">
         <is>
-          <t>1 MB</t>
+          <t>64 KB</t>
         </is>
       </c>
       <c r="F89" s="27" t="n">
-        <v>1088.4</v>
+        <v>587.1</v>
       </c>
       <c r="G89" s="27" t="n">
-        <v>0.9188</v>
+        <v>1.7033</v>
       </c>
       <c r="H89" s="27" t="n">
-        <v>1088.43</v>
+        <v>36.69</v>
       </c>
       <c r="I89" s="26" t="inlineStr"/>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="B90" s="26" t="inlineStr">
         <is>
-          <t>HMAC_SHA384</t>
+          <t>HMAC_SHA512</t>
         </is>
       </c>
       <c r="C90" s="26" t="inlineStr">
@@ -5475,7 +5475,7 @@
         </is>
       </c>
       <c r="D90" s="26" t="n">
-        <v>384</v>
+        <v>512</v>
       </c>
       <c r="E90" s="26" t="inlineStr">
         <is>
@@ -5483,13 +5483,13 @@
         </is>
       </c>
       <c r="F90" s="27" t="n">
-        <v>7466.8</v>
+        <v>584.1</v>
       </c>
       <c r="G90" s="27" t="n">
-        <v>0.1339</v>
+        <v>1.7121</v>
       </c>
       <c r="H90" s="27" t="n">
-        <v>466.68</v>
+        <v>36.51</v>
       </c>
       <c r="I90" s="26" t="inlineStr"/>
     </row>
@@ -5514,17 +5514,17 @@
       </c>
       <c r="E91" s="26" t="inlineStr">
         <is>
-          <t>64 KB</t>
+          <t>1 MB</t>
         </is>
       </c>
       <c r="F91" s="27" t="n">
-        <v>7585.3</v>
+        <v>38.8</v>
       </c>
       <c r="G91" s="27" t="n">
-        <v>0.1318</v>
+        <v>25.8014</v>
       </c>
       <c r="H91" s="27" t="n">
-        <v>474.08</v>
+        <v>38.76</v>
       </c>
       <c r="I91" s="26" t="inlineStr"/>
     </row>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="B92" s="26" t="inlineStr">
         <is>
-          <t>HMAC_SHA512</t>
+          <t>AES_CMAC</t>
         </is>
       </c>
       <c r="C92" s="26" t="inlineStr">
@@ -5545,21 +5545,21 @@
         </is>
       </c>
       <c r="D92" s="26" t="n">
-        <v>512</v>
+        <v>128</v>
       </c>
       <c r="E92" s="26" t="inlineStr">
         <is>
-          <t>1 MB</t>
+          <t>64 B</t>
         </is>
       </c>
       <c r="F92" s="27" t="n">
-        <v>521.1</v>
+        <v>13091.1</v>
       </c>
       <c r="G92" s="27" t="n">
-        <v>1.919</v>
+        <v>0.0764</v>
       </c>
       <c r="H92" s="27" t="n">
-        <v>521.11</v>
+        <v>0.8</v>
       </c>
       <c r="I92" s="26" t="inlineStr"/>
     </row>
@@ -5584,17 +5584,17 @@
       </c>
       <c r="E93" s="26" t="inlineStr">
         <is>
-          <t>64 B</t>
+          <t>1 KB</t>
         </is>
       </c>
       <c r="F93" s="27" t="n">
-        <v>72528.5</v>
+        <v>9997.799999999999</v>
       </c>
       <c r="G93" s="27" t="n">
-        <v>0.0138</v>
+        <v>0.1</v>
       </c>
       <c r="H93" s="27" t="n">
-        <v>4.43</v>
+        <v>9.76</v>
       </c>
       <c r="I93" s="26" t="inlineStr"/>
     </row>
@@ -5619,17 +5619,17 @@
       </c>
       <c r="E94" s="26" t="inlineStr">
         <is>
-          <t>1 KB</t>
+          <t>64 KB</t>
         </is>
       </c>
       <c r="F94" s="27" t="n">
-        <v>66169</v>
+        <v>609.2</v>
       </c>
       <c r="G94" s="27" t="n">
-        <v>0.0151</v>
+        <v>1.6415</v>
       </c>
       <c r="H94" s="27" t="n">
-        <v>64.62</v>
+        <v>38.07</v>
       </c>
       <c r="I94" s="26" t="inlineStr"/>
     </row>
@@ -5641,7 +5641,7 @@
       </c>
       <c r="B95" s="26" t="inlineStr">
         <is>
-          <t>AES_CMAC</t>
+          <t>DES3_CMAC</t>
         </is>
       </c>
       <c r="C95" s="26" t="inlineStr">
@@ -5650,21 +5650,21 @@
         </is>
       </c>
       <c r="D95" s="26" t="n">
-        <v>128</v>
+        <v>168</v>
       </c>
       <c r="E95" s="26" t="inlineStr">
         <is>
-          <t>64 KB</t>
+          <t>64 B</t>
         </is>
       </c>
       <c r="F95" s="27" t="n">
-        <v>9931.200000000001</v>
+        <v>12715.4</v>
       </c>
       <c r="G95" s="27" t="n">
-        <v>0.1007</v>
+        <v>0.0786</v>
       </c>
       <c r="H95" s="27" t="n">
-        <v>620.7</v>
+        <v>0.78</v>
       </c>
       <c r="I95" s="26" t="inlineStr"/>
     </row>
@@ -5689,17 +5689,17 @@
       </c>
       <c r="E96" s="26" t="inlineStr">
         <is>
-          <t>64 B</t>
+          <t>1 KB</t>
         </is>
       </c>
       <c r="F96" s="27" t="n">
-        <v>55220.3</v>
+        <v>6851.2</v>
       </c>
       <c r="G96" s="27" t="n">
-        <v>0.0181</v>
+        <v>0.146</v>
       </c>
       <c r="H96" s="27" t="n">
-        <v>3.37</v>
+        <v>6.69</v>
       </c>
       <c r="I96" s="26" t="inlineStr"/>
     </row>
@@ -5724,57 +5724,57 @@
       </c>
       <c r="E97" s="26" t="inlineStr">
         <is>
+          <t>64 KB</t>
+        </is>
+      </c>
+      <c r="F97" s="27" t="n">
+        <v>235</v>
+      </c>
+      <c r="G97" s="27" t="n">
+        <v>4.2549</v>
+      </c>
+      <c r="H97" s="27" t="n">
+        <v>14.69</v>
+      </c>
+      <c r="I97" s="26" t="inlineStr"/>
+    </row>
+    <row r="98" ht="16" customHeight="1">
+      <c r="A98" s="28" t="inlineStr">
+        <is>
+          <t>Digest</t>
+        </is>
+      </c>
+      <c r="B98" s="29" t="inlineStr">
+        <is>
+          <t>SHA1</t>
+        </is>
+      </c>
+      <c r="C98" s="29" t="inlineStr">
+        <is>
+          <t>digest</t>
+        </is>
+      </c>
+      <c r="D98" s="29" t="n">
+        <v>160</v>
+      </c>
+      <c r="E98" s="29" t="inlineStr">
+        <is>
           <t>1 KB</t>
         </is>
       </c>
-      <c r="F97" s="27" t="n">
-        <v>16280.2</v>
-      </c>
-      <c r="G97" s="27" t="n">
-        <v>0.0614</v>
-      </c>
-      <c r="H97" s="27" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="I97" s="26" t="inlineStr"/>
-    </row>
-    <row r="98" ht="16" customHeight="1">
-      <c r="A98" s="26" t="inlineStr">
-        <is>
-          <t>HMAC</t>
-        </is>
-      </c>
-      <c r="B98" s="26" t="inlineStr">
-        <is>
-          <t>DES3_CMAC</t>
-        </is>
-      </c>
-      <c r="C98" s="26" t="inlineStr">
-        <is>
-          <t>sign</t>
-        </is>
-      </c>
-      <c r="D98" s="26" t="n">
-        <v>168</v>
-      </c>
-      <c r="E98" s="26" t="inlineStr">
-        <is>
-          <t>64 KB</t>
-        </is>
-      </c>
-      <c r="F98" s="27" t="n">
-        <v>347.8</v>
-      </c>
-      <c r="G98" s="27" t="n">
-        <v>2.8754</v>
-      </c>
-      <c r="H98" s="27" t="n">
-        <v>21.74</v>
-      </c>
-      <c r="I98" s="26" t="inlineStr"/>
+      <c r="F98" s="30" t="n">
+        <v>24773.9</v>
+      </c>
+      <c r="G98" s="30" t="n">
+        <v>0.0404</v>
+      </c>
+      <c r="H98" s="30" t="n">
+        <v>24.19</v>
+      </c>
+      <c r="I98" s="29" t="inlineStr"/>
     </row>
     <row r="99" ht="16" customHeight="1">
-      <c r="A99" s="28" t="inlineStr">
+      <c r="A99" s="29" t="inlineStr">
         <is>
           <t>Digest</t>
         </is>
@@ -5794,17 +5794,17 @@
       </c>
       <c r="E99" s="29" t="inlineStr">
         <is>
-          <t>1 KB</t>
+          <t>64 KB</t>
         </is>
       </c>
       <c r="F99" s="30" t="n">
-        <v>164514.7</v>
+        <v>606.4</v>
       </c>
       <c r="G99" s="30" t="n">
-        <v>0.0061</v>
+        <v>1.6491</v>
       </c>
       <c r="H99" s="30" t="n">
-        <v>160.66</v>
+        <v>37.9</v>
       </c>
       <c r="I99" s="29" t="inlineStr"/>
     </row>
@@ -5829,17 +5829,17 @@
       </c>
       <c r="E100" s="29" t="inlineStr">
         <is>
-          <t>64 KB</t>
+          <t>1 MB</t>
         </is>
       </c>
       <c r="F100" s="30" t="n">
-        <v>18406.3</v>
+        <v>39.9</v>
       </c>
       <c r="G100" s="30" t="n">
-        <v>0.0543</v>
+        <v>25.0385</v>
       </c>
       <c r="H100" s="30" t="n">
-        <v>1150.4</v>
+        <v>39.94</v>
       </c>
       <c r="I100" s="29" t="inlineStr"/>
     </row>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="B101" s="29" t="inlineStr">
         <is>
-          <t>SHA1</t>
+          <t>SHA256</t>
         </is>
       </c>
       <c r="C101" s="29" t="inlineStr">
@@ -5860,21 +5860,21 @@
         </is>
       </c>
       <c r="D101" s="29" t="n">
-        <v>160</v>
+        <v>256</v>
       </c>
       <c r="E101" s="29" t="inlineStr">
         <is>
-          <t>1 MB</t>
+          <t>1 KB</t>
         </is>
       </c>
       <c r="F101" s="30" t="n">
-        <v>1173.5</v>
+        <v>24221.3</v>
       </c>
       <c r="G101" s="30" t="n">
-        <v>0.8522</v>
+        <v>0.0413</v>
       </c>
       <c r="H101" s="30" t="n">
-        <v>1173.5</v>
+        <v>23.65</v>
       </c>
       <c r="I101" s="29" t="inlineStr"/>
     </row>
@@ -5899,17 +5899,17 @@
       </c>
       <c r="E102" s="29" t="inlineStr">
         <is>
-          <t>1 KB</t>
+          <t>64 KB</t>
         </is>
       </c>
       <c r="F102" s="30" t="n">
-        <v>33427.6</v>
+        <v>592</v>
       </c>
       <c r="G102" s="30" t="n">
-        <v>0.0299</v>
+        <v>1.6891</v>
       </c>
       <c r="H102" s="30" t="n">
-        <v>32.64</v>
+        <v>37</v>
       </c>
       <c r="I102" s="29" t="inlineStr"/>
     </row>
@@ -5934,17 +5934,17 @@
       </c>
       <c r="E103" s="29" t="inlineStr">
         <is>
-          <t>64 KB</t>
+          <t>1 MB</t>
         </is>
       </c>
       <c r="F103" s="30" t="n">
-        <v>12020.3</v>
+        <v>37.4</v>
       </c>
       <c r="G103" s="30" t="n">
-        <v>0.0832</v>
+        <v>26.7101</v>
       </c>
       <c r="H103" s="30" t="n">
-        <v>751.27</v>
+        <v>37.44</v>
       </c>
       <c r="I103" s="29" t="inlineStr"/>
     </row>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="B104" s="29" t="inlineStr">
         <is>
-          <t>SHA256</t>
+          <t>SHA384</t>
         </is>
       </c>
       <c r="C104" s="29" t="inlineStr">
@@ -5965,21 +5965,21 @@
         </is>
       </c>
       <c r="D104" s="29" t="n">
-        <v>256</v>
+        <v>384</v>
       </c>
       <c r="E104" s="29" t="inlineStr">
         <is>
-          <t>1 MB</t>
+          <t>64 KB</t>
         </is>
       </c>
       <c r="F104" s="30" t="n">
-        <v>782.2</v>
+        <v>606.3</v>
       </c>
       <c r="G104" s="30" t="n">
-        <v>1.2784</v>
+        <v>1.6493</v>
       </c>
       <c r="H104" s="30" t="n">
-        <v>782.24</v>
+        <v>37.89</v>
       </c>
       <c r="I104" s="29" t="inlineStr"/>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="B105" s="29" t="inlineStr">
         <is>
-          <t>SHA384</t>
+          <t>SHA512</t>
         </is>
       </c>
       <c r="C105" s="29" t="inlineStr">
@@ -6000,7 +6000,7 @@
         </is>
       </c>
       <c r="D105" s="29" t="n">
-        <v>384</v>
+        <v>512</v>
       </c>
       <c r="E105" s="29" t="inlineStr">
         <is>
@@ -6008,13 +6008,13 @@
         </is>
       </c>
       <c r="F105" s="30" t="n">
-        <v>4967.6</v>
+        <v>590.4</v>
       </c>
       <c r="G105" s="30" t="n">
-        <v>0.2013</v>
+        <v>1.6938</v>
       </c>
       <c r="H105" s="30" t="n">
-        <v>310.47</v>
+        <v>36.9</v>
       </c>
       <c r="I105" s="29" t="inlineStr"/>
     </row>
@@ -6039,57 +6039,59 @@
       </c>
       <c r="E106" s="29" t="inlineStr">
         <is>
-          <t>64 KB</t>
+          <t>1 MB</t>
         </is>
       </c>
       <c r="F106" s="30" t="n">
-        <v>5216.2</v>
+        <v>38.4</v>
       </c>
       <c r="G106" s="30" t="n">
-        <v>0.1917</v>
+        <v>26.039</v>
       </c>
       <c r="H106" s="30" t="n">
-        <v>326.01</v>
+        <v>38.4</v>
       </c>
       <c r="I106" s="29" t="inlineStr"/>
     </row>
     <row r="107" ht="16" customHeight="1">
-      <c r="A107" s="29" t="inlineStr">
-        <is>
-          <t>Digest</t>
-        </is>
-      </c>
-      <c r="B107" s="29" t="inlineStr">
-        <is>
-          <t>SHA512</t>
-        </is>
-      </c>
-      <c r="C107" s="29" t="inlineStr">
-        <is>
-          <t>digest</t>
-        </is>
-      </c>
-      <c r="D107" s="29" t="n">
-        <v>512</v>
-      </c>
-      <c r="E107" s="29" t="inlineStr">
-        <is>
-          <t>1 MB</t>
-        </is>
-      </c>
-      <c r="F107" s="30" t="n">
-        <v>350.1</v>
-      </c>
-      <c r="G107" s="30" t="n">
-        <v>2.8565</v>
-      </c>
-      <c r="H107" s="30" t="n">
-        <v>350.08</v>
-      </c>
-      <c r="I107" s="29" t="inlineStr"/>
+      <c r="A107" s="31" t="inlineStr">
+        <is>
+          <t>KeyGen</t>
+        </is>
+      </c>
+      <c r="B107" s="32" t="inlineStr">
+        <is>
+          <t>AES_KEY_GEN</t>
+        </is>
+      </c>
+      <c r="C107" s="32" t="inlineStr">
+        <is>
+          <t>keygen</t>
+        </is>
+      </c>
+      <c r="D107" s="32" t="n">
+        <v>128</v>
+      </c>
+      <c r="E107" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F107" s="33" t="n">
+        <v>1618.1</v>
+      </c>
+      <c r="G107" s="33" t="n">
+        <v>0.618</v>
+      </c>
+      <c r="H107" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I107" s="32" t="inlineStr"/>
     </row>
     <row r="108" ht="16" customHeight="1">
-      <c r="A108" s="31" t="inlineStr">
+      <c r="A108" s="32" t="inlineStr">
         <is>
           <t>KeyGen</t>
         </is>
@@ -6105,7 +6107,7 @@
         </is>
       </c>
       <c r="D108" s="32" t="n">
-        <v>128</v>
+        <v>192</v>
       </c>
       <c r="E108" s="32" t="inlineStr">
         <is>
@@ -6113,10 +6115,10 @@
         </is>
       </c>
       <c r="F108" s="33" t="n">
-        <v>5425.6</v>
+        <v>1242.9</v>
       </c>
       <c r="G108" s="33" t="n">
-        <v>0.1843</v>
+        <v>0.8046</v>
       </c>
       <c r="H108" s="33" t="inlineStr">
         <is>
@@ -6142,7 +6144,7 @@
         </is>
       </c>
       <c r="D109" s="32" t="n">
-        <v>192</v>
+        <v>256</v>
       </c>
       <c r="E109" s="32" t="inlineStr">
         <is>
@@ -6150,10 +6152,10 @@
         </is>
       </c>
       <c r="F109" s="33" t="n">
-        <v>4901.8</v>
+        <v>1592.8</v>
       </c>
       <c r="G109" s="33" t="n">
-        <v>0.204</v>
+        <v>0.6278</v>
       </c>
       <c r="H109" s="33" t="inlineStr">
         <is>
@@ -6170,7 +6172,7 @@
       </c>
       <c r="B110" s="32" t="inlineStr">
         <is>
-          <t>AES_KEY_GEN</t>
+          <t>DES3_KEY_GEN</t>
         </is>
       </c>
       <c r="C110" s="32" t="inlineStr">
@@ -6179,7 +6181,7 @@
         </is>
       </c>
       <c r="D110" s="32" t="n">
-        <v>256</v>
+        <v>168</v>
       </c>
       <c r="E110" s="32" t="inlineStr">
         <is>
@@ -6187,10 +6189,10 @@
         </is>
       </c>
       <c r="F110" s="33" t="n">
-        <v>5514.3</v>
+        <v>1635</v>
       </c>
       <c r="G110" s="33" t="n">
-        <v>0.1813</v>
+        <v>0.6116</v>
       </c>
       <c r="H110" s="33" t="inlineStr">
         <is>
@@ -6207,7 +6209,7 @@
       </c>
       <c r="B111" s="32" t="inlineStr">
         <is>
-          <t>DES3_KEY_GEN</t>
+          <t>GENERIC_SECRET_KEY_GEN</t>
         </is>
       </c>
       <c r="C111" s="32" t="inlineStr">
@@ -6216,7 +6218,7 @@
         </is>
       </c>
       <c r="D111" s="32" t="n">
-        <v>168</v>
+        <v>256</v>
       </c>
       <c r="E111" s="32" t="inlineStr">
         <is>
@@ -6224,10 +6226,10 @@
         </is>
       </c>
       <c r="F111" s="33" t="n">
-        <v>3735.8</v>
+        <v>1728</v>
       </c>
       <c r="G111" s="33" t="n">
-        <v>0.2677</v>
+        <v>0.5787</v>
       </c>
       <c r="H111" s="33" t="inlineStr">
         <is>
@@ -6244,7 +6246,7 @@
       </c>
       <c r="B112" s="32" t="inlineStr">
         <is>
-          <t>GENERIC_SECRET_KEY_GEN</t>
+          <t>EC_KEY_PAIR_GEN</t>
         </is>
       </c>
       <c r="C112" s="32" t="inlineStr">
@@ -6261,10 +6263,10 @@
         </is>
       </c>
       <c r="F112" s="33" t="n">
-        <v>6511.2</v>
+        <v>860</v>
       </c>
       <c r="G112" s="33" t="n">
-        <v>0.1536</v>
+        <v>1.1628</v>
       </c>
       <c r="H112" s="33" t="inlineStr">
         <is>
@@ -6290,7 +6292,7 @@
         </is>
       </c>
       <c r="D113" s="32" t="n">
-        <v>256</v>
+        <v>384</v>
       </c>
       <c r="E113" s="32" t="inlineStr">
         <is>
@@ -6298,10 +6300,10 @@
         </is>
       </c>
       <c r="F113" s="33" t="n">
-        <v>2274.5</v>
+        <v>402.8</v>
       </c>
       <c r="G113" s="33" t="n">
-        <v>0.4396</v>
+        <v>2.4829</v>
       </c>
       <c r="H113" s="33" t="inlineStr">
         <is>
@@ -6318,7 +6320,7 @@
       </c>
       <c r="B114" s="32" t="inlineStr">
         <is>
-          <t>EC_KEY_PAIR_GEN</t>
+          <t>RSA_PKCS_KEY_PAIR_GEN</t>
         </is>
       </c>
       <c r="C114" s="32" t="inlineStr">
@@ -6327,7 +6329,7 @@
         </is>
       </c>
       <c r="D114" s="32" t="n">
-        <v>384</v>
+        <v>2048</v>
       </c>
       <c r="E114" s="32" t="inlineStr">
         <is>
@@ -6335,10 +6337,10 @@
         </is>
       </c>
       <c r="F114" s="33" t="n">
-        <v>738.7</v>
+        <v>5.3</v>
       </c>
       <c r="G114" s="33" t="n">
-        <v>1.3538</v>
+        <v>187.0991</v>
       </c>
       <c r="H114" s="33" t="inlineStr">
         <is>
@@ -6364,7 +6366,7 @@
         </is>
       </c>
       <c r="D115" s="32" t="n">
-        <v>2048</v>
+        <v>4096</v>
       </c>
       <c r="E115" s="32" t="inlineStr">
         <is>
@@ -6372,10 +6374,10 @@
         </is>
       </c>
       <c r="F115" s="33" t="n">
-        <v>4.8</v>
+        <v>0.8</v>
       </c>
       <c r="G115" s="33" t="n">
-        <v>207.0319</v>
+        <v>1260.1927</v>
       </c>
       <c r="H115" s="33" t="inlineStr">
         <is>
@@ -6392,7 +6394,7 @@
       </c>
       <c r="B116" s="32" t="inlineStr">
         <is>
-          <t>RSA_PKCS_KEY_PAIR_GEN</t>
+          <t>EC_EDWARDS_KEY_PAIR_GEN</t>
         </is>
       </c>
       <c r="C116" s="32" t="inlineStr">
@@ -6401,7 +6403,7 @@
         </is>
       </c>
       <c r="D116" s="32" t="n">
-        <v>4096</v>
+        <v>256</v>
       </c>
       <c r="E116" s="32" t="inlineStr">
         <is>
@@ -6409,10 +6411,10 @@
         </is>
       </c>
       <c r="F116" s="33" t="n">
-        <v>0.8</v>
+        <v>756.4</v>
       </c>
       <c r="G116" s="33" t="n">
-        <v>1210.8194</v>
+        <v>1.3221</v>
       </c>
       <c r="H116" s="33" t="inlineStr">
         <is>
@@ -6422,51 +6424,51 @@
       <c r="I116" s="32" t="inlineStr"/>
     </row>
     <row r="117" ht="16" customHeight="1">
-      <c r="A117" s="32" t="inlineStr">
-        <is>
-          <t>KeyGen</t>
-        </is>
-      </c>
-      <c r="B117" s="32" t="inlineStr">
-        <is>
-          <t>EC_EDWARDS_KEY_PAIR_GEN</t>
-        </is>
-      </c>
-      <c r="C117" s="32" t="inlineStr">
-        <is>
-          <t>keygen</t>
-        </is>
-      </c>
-      <c r="D117" s="32" t="n">
+      <c r="A117" s="34" t="inlineStr">
+        <is>
+          <t>KeyWrap</t>
+        </is>
+      </c>
+      <c r="B117" s="35" t="inlineStr">
+        <is>
+          <t>AES_KEY_WRAP</t>
+        </is>
+      </c>
+      <c r="C117" s="35" t="inlineStr">
+        <is>
+          <t>wrap</t>
+        </is>
+      </c>
+      <c r="D117" s="35" t="n">
         <v>256</v>
       </c>
-      <c r="E117" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F117" s="33" t="n">
-        <v>1841.2</v>
-      </c>
-      <c r="G117" s="33" t="n">
-        <v>0.5431</v>
-      </c>
-      <c r="H117" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I117" s="32" t="inlineStr"/>
+      <c r="E117" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F117" s="36" t="n">
+        <v>4968.8</v>
+      </c>
+      <c r="G117" s="36" t="n">
+        <v>0.2013</v>
+      </c>
+      <c r="H117" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I117" s="35" t="inlineStr"/>
     </row>
     <row r="118" ht="16" customHeight="1">
-      <c r="A118" s="34" t="inlineStr">
+      <c r="A118" s="35" t="inlineStr">
         <is>
           <t>KeyWrap</t>
         </is>
       </c>
       <c r="B118" s="35" t="inlineStr">
         <is>
-          <t>AES_KEY_WRAP</t>
+          <t>AES_KEY_WRAP_PAD</t>
         </is>
       </c>
       <c r="C118" s="35" t="inlineStr">
@@ -6483,10 +6485,10 @@
         </is>
       </c>
       <c r="F118" s="36" t="n">
-        <v>33800.3</v>
+        <v>4990.5</v>
       </c>
       <c r="G118" s="36" t="n">
-        <v>0.0296</v>
+        <v>0.2004</v>
       </c>
       <c r="H118" s="36" t="inlineStr">
         <is>
@@ -6495,45 +6497,8 @@
       </c>
       <c r="I118" s="35" t="inlineStr"/>
     </row>
-    <row r="119" ht="16" customHeight="1">
-      <c r="A119" s="35" t="inlineStr">
-        <is>
-          <t>KeyWrap</t>
-        </is>
-      </c>
-      <c r="B119" s="35" t="inlineStr">
-        <is>
-          <t>AES_KEY_WRAP_PAD</t>
-        </is>
-      </c>
-      <c r="C119" s="35" t="inlineStr">
-        <is>
-          <t>wrap</t>
-        </is>
-      </c>
-      <c r="D119" s="35" t="n">
-        <v>256</v>
-      </c>
-      <c r="E119" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F119" s="36" t="n">
-        <v>32178.5</v>
-      </c>
-      <c r="G119" s="36" t="n">
-        <v>0.0311</v>
-      </c>
-      <c r="H119" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I119" s="35" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:I119"/>
+  <autoFilter ref="A3:I118"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
@@ -6641,13 +6606,13 @@
         </is>
       </c>
       <c r="F3" s="30" t="n">
-        <v>164514.7</v>
+        <v>24773.9</v>
       </c>
       <c r="G3" s="30" t="n">
-        <v>0.0061</v>
+        <v>0.0404</v>
       </c>
       <c r="H3" s="30" t="n">
-        <v>160.66</v>
+        <v>24.19</v>
       </c>
       <c r="I3" s="29" t="inlineStr"/>
     </row>
@@ -6676,13 +6641,13 @@
         </is>
       </c>
       <c r="F4" s="30" t="n">
-        <v>18406.3</v>
+        <v>606.4</v>
       </c>
       <c r="G4" s="30" t="n">
-        <v>0.0543</v>
+        <v>1.6491</v>
       </c>
       <c r="H4" s="30" t="n">
-        <v>1150.4</v>
+        <v>37.9</v>
       </c>
       <c r="I4" s="29" t="inlineStr"/>
     </row>
@@ -6711,13 +6676,13 @@
         </is>
       </c>
       <c r="F5" s="30" t="n">
-        <v>1173.5</v>
+        <v>39.9</v>
       </c>
       <c r="G5" s="30" t="n">
-        <v>0.8522</v>
+        <v>25.0385</v>
       </c>
       <c r="H5" s="30" t="n">
-        <v>1173.5</v>
+        <v>39.94</v>
       </c>
       <c r="I5" s="29" t="inlineStr"/>
     </row>
@@ -6746,13 +6711,13 @@
         </is>
       </c>
       <c r="F6" s="30" t="n">
-        <v>33427.6</v>
+        <v>24221.3</v>
       </c>
       <c r="G6" s="30" t="n">
-        <v>0.0299</v>
+        <v>0.0413</v>
       </c>
       <c r="H6" s="30" t="n">
-        <v>32.64</v>
+        <v>23.65</v>
       </c>
       <c r="I6" s="29" t="inlineStr"/>
     </row>
@@ -6781,13 +6746,13 @@
         </is>
       </c>
       <c r="F7" s="30" t="n">
-        <v>12020.3</v>
+        <v>592</v>
       </c>
       <c r="G7" s="30" t="n">
-        <v>0.0832</v>
+        <v>1.6891</v>
       </c>
       <c r="H7" s="30" t="n">
-        <v>751.27</v>
+        <v>37</v>
       </c>
       <c r="I7" s="29" t="inlineStr"/>
     </row>
@@ -6816,13 +6781,13 @@
         </is>
       </c>
       <c r="F8" s="30" t="n">
-        <v>782.2</v>
+        <v>37.4</v>
       </c>
       <c r="G8" s="30" t="n">
-        <v>1.2784</v>
+        <v>26.7101</v>
       </c>
       <c r="H8" s="30" t="n">
-        <v>782.24</v>
+        <v>37.44</v>
       </c>
       <c r="I8" s="29" t="inlineStr"/>
     </row>
@@ -6851,13 +6816,13 @@
         </is>
       </c>
       <c r="F9" s="30" t="n">
-        <v>4967.6</v>
+        <v>606.3</v>
       </c>
       <c r="G9" s="30" t="n">
-        <v>0.2013</v>
+        <v>1.6493</v>
       </c>
       <c r="H9" s="30" t="n">
-        <v>310.47</v>
+        <v>37.89</v>
       </c>
       <c r="I9" s="29" t="inlineStr"/>
     </row>
@@ -6886,13 +6851,13 @@
         </is>
       </c>
       <c r="F10" s="30" t="n">
-        <v>5216.2</v>
+        <v>590.4</v>
       </c>
       <c r="G10" s="30" t="n">
-        <v>0.1917</v>
+        <v>1.6938</v>
       </c>
       <c r="H10" s="30" t="n">
-        <v>326.01</v>
+        <v>36.9</v>
       </c>
       <c r="I10" s="29" t="inlineStr"/>
     </row>
@@ -6921,13 +6886,13 @@
         </is>
       </c>
       <c r="F11" s="30" t="n">
-        <v>350.1</v>
+        <v>38.4</v>
       </c>
       <c r="G11" s="30" t="n">
-        <v>2.8565</v>
+        <v>26.039</v>
       </c>
       <c r="H11" s="30" t="n">
-        <v>350.08</v>
+        <v>38.4</v>
       </c>
       <c r="I11" s="29" t="inlineStr"/>
     </row>
@@ -6950,7 +6915,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>164514.7</v>
+        <v>24773.9</v>
       </c>
     </row>
     <row r="16">
@@ -6960,7 +6925,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18406.3</v>
+        <v>606.4</v>
       </c>
     </row>
     <row r="17">
@@ -6970,7 +6935,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1173.5</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="18">
@@ -6980,7 +6945,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>33427.6</v>
+        <v>24221.3</v>
       </c>
     </row>
     <row r="19">
@@ -6990,7 +6955,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>12020.3</v>
+        <v>592</v>
       </c>
     </row>
     <row r="20">
@@ -7000,7 +6965,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>782.2</v>
+        <v>37.4</v>
       </c>
     </row>
     <row r="21">
@@ -7010,7 +6975,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4967.6</v>
+        <v>606.3</v>
       </c>
     </row>
     <row r="22">
@@ -7020,7 +6985,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5216.2</v>
+        <v>590.4</v>
       </c>
     </row>
     <row r="23">
@@ -7030,7 +6995,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>350.1</v>
+        <v>38.4</v>
       </c>
     </row>
   </sheetData>
@@ -7142,10 +7107,10 @@
         </is>
       </c>
       <c r="F3" s="33" t="n">
-        <v>5425.6</v>
+        <v>1618.1</v>
       </c>
       <c r="G3" s="33" t="n">
-        <v>0.1843</v>
+        <v>0.618</v>
       </c>
       <c r="H3" s="33" t="inlineStr">
         <is>
@@ -7179,10 +7144,10 @@
         </is>
       </c>
       <c r="F4" s="33" t="n">
-        <v>4901.8</v>
+        <v>1242.9</v>
       </c>
       <c r="G4" s="33" t="n">
-        <v>0.204</v>
+        <v>0.8046</v>
       </c>
       <c r="H4" s="33" t="inlineStr">
         <is>
@@ -7216,10 +7181,10 @@
         </is>
       </c>
       <c r="F5" s="33" t="n">
-        <v>5514.3</v>
+        <v>1592.8</v>
       </c>
       <c r="G5" s="33" t="n">
-        <v>0.1813</v>
+        <v>0.6278</v>
       </c>
       <c r="H5" s="33" t="inlineStr">
         <is>
@@ -7253,10 +7218,10 @@
         </is>
       </c>
       <c r="F6" s="33" t="n">
-        <v>3735.8</v>
+        <v>1635</v>
       </c>
       <c r="G6" s="33" t="n">
-        <v>0.2677</v>
+        <v>0.6116</v>
       </c>
       <c r="H6" s="33" t="inlineStr">
         <is>
@@ -7290,10 +7255,10 @@
         </is>
       </c>
       <c r="F7" s="33" t="n">
-        <v>6511.2</v>
+        <v>1728</v>
       </c>
       <c r="G7" s="33" t="n">
-        <v>0.1536</v>
+        <v>0.5787</v>
       </c>
       <c r="H7" s="33" t="inlineStr">
         <is>
@@ -7327,10 +7292,10 @@
         </is>
       </c>
       <c r="F8" s="33" t="n">
-        <v>2274.5</v>
+        <v>860</v>
       </c>
       <c r="G8" s="33" t="n">
-        <v>0.4396</v>
+        <v>1.1628</v>
       </c>
       <c r="H8" s="33" t="inlineStr">
         <is>
@@ -7364,10 +7329,10 @@
         </is>
       </c>
       <c r="F9" s="33" t="n">
-        <v>738.7</v>
+        <v>402.8</v>
       </c>
       <c r="G9" s="33" t="n">
-        <v>1.3538</v>
+        <v>2.4829</v>
       </c>
       <c r="H9" s="33" t="inlineStr">
         <is>
@@ -7401,10 +7366,10 @@
         </is>
       </c>
       <c r="F10" s="33" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="G10" s="33" t="n">
-        <v>207.0319</v>
+        <v>187.0991</v>
       </c>
       <c r="H10" s="33" t="inlineStr">
         <is>
@@ -7441,7 +7406,7 @@
         <v>0.8</v>
       </c>
       <c r="G11" s="33" t="n">
-        <v>1210.8194</v>
+        <v>1260.1927</v>
       </c>
       <c r="H11" s="33" t="inlineStr">
         <is>
@@ -7475,10 +7440,10 @@
         </is>
       </c>
       <c r="F12" s="33" t="n">
-        <v>1841.2</v>
+        <v>756.4</v>
       </c>
       <c r="G12" s="33" t="n">
-        <v>0.5431</v>
+        <v>1.3221</v>
       </c>
       <c r="H12" s="33" t="inlineStr">
         <is>
@@ -7506,7 +7471,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5425.6</v>
+        <v>1618.1</v>
       </c>
     </row>
     <row r="17">
@@ -7516,7 +7481,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4901.8</v>
+        <v>1242.9</v>
       </c>
     </row>
     <row r="18">
@@ -7526,7 +7491,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5514.3</v>
+        <v>1592.8</v>
       </c>
     </row>
     <row r="19">
@@ -7536,7 +7501,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3735.8</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="20">
@@ -7546,7 +7511,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6511.2</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="21">
@@ -7556,7 +7521,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2274.5</v>
+        <v>860</v>
       </c>
     </row>
     <row r="22">
@@ -7566,7 +7531,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>738.7</v>
+        <v>402.8</v>
       </c>
     </row>
     <row r="23">
@@ -7576,7 +7541,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="24">
@@ -7596,7 +7561,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1841.2</v>
+        <v>756.4</v>
       </c>
     </row>
   </sheetData>
@@ -7708,10 +7673,10 @@
         </is>
       </c>
       <c r="F3" s="36" t="n">
-        <v>33800.3</v>
+        <v>4968.8</v>
       </c>
       <c r="G3" s="36" t="n">
-        <v>0.0296</v>
+        <v>0.2013</v>
       </c>
       <c r="H3" s="36" t="inlineStr">
         <is>
@@ -7745,10 +7710,10 @@
         </is>
       </c>
       <c r="F4" s="36" t="n">
-        <v>32178.5</v>
+        <v>4990.5</v>
       </c>
       <c r="G4" s="36" t="n">
-        <v>0.0311</v>
+        <v>0.2004</v>
       </c>
       <c r="H4" s="36" t="inlineStr">
         <is>
@@ -7776,7 +7741,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>33800.3</v>
+        <v>4968.8</v>
       </c>
     </row>
     <row r="9">
@@ -7786,7 +7751,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32178.5</v>
+        <v>4990.5</v>
       </c>
     </row>
   </sheetData>
@@ -7805,7 +7770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -7838,7 +7803,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>76377.89999999999</v>
+        <v>11150.1</v>
       </c>
     </row>
     <row r="4">
@@ -7848,7 +7813,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>73947.89999999999</v>
+        <v>11064.9</v>
       </c>
     </row>
     <row r="5">
@@ -7858,7 +7823,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>72528.5</v>
+        <v>13091.1</v>
       </c>
     </row>
     <row r="6">
@@ -7868,7 +7833,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>61154</v>
+        <v>7604</v>
       </c>
     </row>
     <row r="7">
@@ -7878,7 +7843,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>76104.60000000001</v>
+        <v>12372.7</v>
       </c>
     </row>
     <row r="8">
@@ -7888,7 +7853,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>61497.1</v>
+        <v>4425.7</v>
       </c>
     </row>
     <row r="9">
@@ -7898,7 +7863,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>62435.2</v>
+        <v>10358.4</v>
       </c>
     </row>
     <row r="10">
@@ -7908,7 +7873,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5514.3</v>
+        <v>1618.1</v>
       </c>
     </row>
     <row r="11">
@@ -7918,7 +7883,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>33800.3</v>
+        <v>4968.8</v>
       </c>
     </row>
     <row r="12">
@@ -7928,7 +7893,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>32178.5</v>
+        <v>4990.5</v>
       </c>
     </row>
     <row r="13">
@@ -7938,7 +7903,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>61158.9</v>
+        <v>11192.5</v>
       </c>
     </row>
     <row r="14">
@@ -7948,7 +7913,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>55220.3</v>
+        <v>12715.4</v>
       </c>
     </row>
     <row r="15">
@@ -7958,7 +7923,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>60446.2</v>
+        <v>11805.6</v>
       </c>
     </row>
     <row r="16">
@@ -7968,7 +7933,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3735.8</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="17">
@@ -7978,7 +7943,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4364.6</v>
+        <v>1174.8</v>
       </c>
     </row>
     <row r="18">
@@ -7988,7 +7953,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4703.5</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="19">
@@ -7998,7 +7963,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10344</v>
+        <v>4712.6</v>
       </c>
     </row>
     <row r="20">
@@ -8008,7 +7973,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4148.2</v>
+        <v>1228.9</v>
       </c>
     </row>
     <row r="21">
@@ -8018,7 +7983,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15954</v>
+        <v>5524</v>
       </c>
     </row>
     <row r="22">
@@ -8028,7 +7993,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>9280.299999999999</v>
+        <v>5522.2</v>
       </c>
     </row>
     <row r="23">
@@ -8038,7 +8003,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1841.2</v>
+        <v>756.4</v>
       </c>
     </row>
     <row r="24">
@@ -8048,7 +8013,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2274.5</v>
+        <v>860</v>
       </c>
     </row>
     <row r="25">
@@ -8058,7 +8023,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4940.8</v>
+        <v>2555.7</v>
       </c>
     </row>
     <row r="26">
@@ -8068,7 +8033,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4622.1</v>
+        <v>2933.2</v>
       </c>
     </row>
     <row r="27">
@@ -8078,7 +8043,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6511.2</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="28">
@@ -8088,7 +8053,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>67043.8</v>
+        <v>9570</v>
       </c>
     </row>
     <row r="29">
@@ -8098,7 +8063,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>70750.7</v>
+        <v>12473.1</v>
       </c>
     </row>
     <row r="30">
@@ -8108,7 +8073,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>7466.8</v>
+        <v>587.1</v>
       </c>
     </row>
     <row r="31">
@@ -8118,7 +8083,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>7585.3</v>
+        <v>584.1</v>
       </c>
     </row>
     <row r="32">
@@ -8128,7 +8093,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="33">
@@ -8138,7 +8103,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1205.2</v>
+        <v>583.4</v>
       </c>
     </row>
     <row r="34">
@@ -8148,7 +8113,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>26587.2</v>
+        <v>8962.4</v>
       </c>
     </row>
     <row r="35">
@@ -8158,7 +8123,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1223.9</v>
+        <v>587.3</v>
       </c>
     </row>
     <row r="36">
@@ -8168,7 +8133,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1151.5</v>
+        <v>571.2</v>
       </c>
     </row>
     <row r="37">
@@ -8178,7 +8143,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>19851.1</v>
+        <v>6707.5</v>
       </c>
     </row>
     <row r="38">
@@ -8188,7 +8153,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1233</v>
+        <v>575.3</v>
       </c>
     </row>
     <row r="39">
@@ -8198,7 +8163,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>22922.8</v>
+        <v>6605.3</v>
       </c>
     </row>
     <row r="40">
@@ -8208,77 +8173,67 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1196.6</v>
+        <v>587</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>RSA_X_509 · encrypt</t>
+          <t>SHA1 · digest</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>25554</v>
+        <v>24773.9</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SHA1 · digest</t>
+          <t>SHA256 · digest</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>164514.7</v>
+        <v>24221.3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SHA256 · digest</t>
+          <t>SHA256_RSA_PKCS · sign</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>33427.6</v>
+        <v>1320.8</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SHA256_RSA_PKCS · sign</t>
+          <t>SHA256_RSA_PKCS · verify</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3425.7</v>
+        <v>8377</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SHA256_RSA_PKCS · verify</t>
+          <t>SHA384 · digest</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>46211.3</v>
+        <v>606.3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SHA384 · digest</t>
+          <t>SHA512 · digest</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4967.6</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>SHA512 · digest</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>5216.2</v>
+        <v>590.4</v>
       </c>
     </row>
   </sheetData>
@@ -8389,13 +8344,13 @@
         </is>
       </c>
       <c r="F3" s="6" t="n">
-        <v>72979.8</v>
+        <v>10815.6</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.0137</v>
+        <v>0.0925</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>4.45</v>
+        <v>0.66</v>
       </c>
       <c r="I3" s="5" t="inlineStr"/>
     </row>
@@ -8424,13 +8379,13 @@
         </is>
       </c>
       <c r="F4" s="6" t="n">
-        <v>66503</v>
+        <v>5566.3</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.015</v>
+        <v>0.1797</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>64.94</v>
+        <v>5.44</v>
       </c>
       <c r="I4" s="5" t="inlineStr"/>
     </row>
@@ -8459,13 +8414,13 @@
         </is>
       </c>
       <c r="F5" s="6" t="n">
-        <v>9831.799999999999</v>
+        <v>167.1</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.1017</v>
+        <v>5.9847</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>614.49</v>
+        <v>10.44</v>
       </c>
       <c r="I5" s="5" t="inlineStr"/>
     </row>
@@ -8494,13 +8449,13 @@
         </is>
       </c>
       <c r="F6" s="6" t="n">
-        <v>336.1</v>
+        <v>10.3</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>2.9755</v>
+        <v>96.7383</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>336.07</v>
+        <v>10.34</v>
       </c>
       <c r="I6" s="5" t="inlineStr"/>
     </row>
@@ -8529,13 +8484,13 @@
         </is>
       </c>
       <c r="F7" s="6" t="n">
-        <v>65721.8</v>
+        <v>5396.6</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.0152</v>
+        <v>0.1853</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>64.18000000000001</v>
+        <v>5.27</v>
       </c>
       <c r="I7" s="5" t="inlineStr"/>
     </row>
@@ -8564,13 +8519,13 @@
         </is>
       </c>
       <c r="F8" s="6" t="n">
-        <v>9036.700000000001</v>
+        <v>169.7</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.1107</v>
+        <v>5.8912</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>564.79</v>
+        <v>10.61</v>
       </c>
       <c r="I8" s="5" t="inlineStr"/>
     </row>
@@ -8599,13 +8554,13 @@
         </is>
       </c>
       <c r="F9" s="6" t="n">
-        <v>73947.89999999999</v>
+        <v>11064.9</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.0135</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>4.51</v>
+        <v>0.68</v>
       </c>
       <c r="I9" s="5" t="inlineStr"/>
     </row>
@@ -8634,13 +8589,13 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>65620.60000000001</v>
+        <v>5628</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.0152</v>
+        <v>0.1777</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>64.08</v>
+        <v>5.5</v>
       </c>
       <c r="I10" s="5" t="inlineStr"/>
     </row>
@@ -8669,13 +8624,13 @@
         </is>
       </c>
       <c r="F11" s="6" t="n">
-        <v>8414.6</v>
+        <v>168.7</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.1188</v>
+        <v>5.9264</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>525.91</v>
+        <v>10.55</v>
       </c>
       <c r="I11" s="5" t="inlineStr"/>
     </row>
@@ -8704,13 +8659,13 @@
         </is>
       </c>
       <c r="F12" s="6" t="n">
-        <v>307.7</v>
+        <v>10.3</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>3.2496</v>
+        <v>97.32850000000001</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>307.73</v>
+        <v>10.27</v>
       </c>
       <c r="I12" s="5" t="inlineStr"/>
     </row>
@@ -8739,13 +8694,13 @@
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>76377.89999999999</v>
+        <v>11150.1</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.0131</v>
+        <v>0.0897</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>4.66</v>
+        <v>0.68</v>
       </c>
       <c r="I13" s="5" t="inlineStr"/>
     </row>
@@ -8774,13 +8729,13 @@
         </is>
       </c>
       <c r="F14" s="6" t="n">
-        <v>67089.10000000001</v>
+        <v>5031.1</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.0149</v>
+        <v>0.1988</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>65.52</v>
+        <v>4.91</v>
       </c>
       <c r="I14" s="5" t="inlineStr"/>
     </row>
@@ -8809,13 +8764,13 @@
         </is>
       </c>
       <c r="F15" s="6" t="n">
-        <v>10771.7</v>
+        <v>143.1</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.09279999999999999</v>
+        <v>6.9874</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>673.23</v>
+        <v>8.94</v>
       </c>
       <c r="I15" s="5" t="inlineStr"/>
     </row>
@@ -8844,13 +8799,13 @@
         </is>
       </c>
       <c r="F16" s="6" t="n">
-        <v>374</v>
+        <v>8.6</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>2.6739</v>
+        <v>116.3753</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>373.99</v>
+        <v>8.59</v>
       </c>
       <c r="I16" s="5" t="inlineStr"/>
     </row>
@@ -8879,13 +8834,13 @@
         </is>
       </c>
       <c r="F17" s="6" t="n">
-        <v>76018.8</v>
+        <v>10438</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.0132</v>
+        <v>0.0958</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>4.64</v>
+        <v>0.64</v>
       </c>
       <c r="I17" s="5" t="inlineStr"/>
     </row>
@@ -8914,13 +8869,13 @@
         </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>64676.3</v>
+        <v>4876.7</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.0155</v>
+        <v>0.2051</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>63.16</v>
+        <v>4.76</v>
       </c>
       <c r="I18" s="5" t="inlineStr"/>
     </row>
@@ -8949,13 +8904,13 @@
         </is>
       </c>
       <c r="F19" s="6" t="n">
-        <v>10895.3</v>
+        <v>140.3</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.09180000000000001</v>
+        <v>7.1273</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>680.96</v>
+        <v>8.77</v>
       </c>
       <c r="I19" s="5" t="inlineStr"/>
     </row>
@@ -8984,13 +8939,13 @@
         </is>
       </c>
       <c r="F20" s="6" t="n">
-        <v>371.5</v>
+        <v>8.6</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>2.6921</v>
+        <v>115.7334</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>371.45</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="I20" s="5" t="inlineStr"/>
     </row>
@@ -9019,13 +8974,13 @@
         </is>
       </c>
       <c r="F21" s="6" t="n">
-        <v>76104.60000000001</v>
+        <v>12372.7</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.0131</v>
+        <v>0.0808</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>4.65</v>
+        <v>0.76</v>
       </c>
       <c r="I21" s="5" t="inlineStr"/>
     </row>
@@ -9054,13 +9009,13 @@
         </is>
       </c>
       <c r="F22" s="6" t="n">
-        <v>70636.7</v>
+        <v>7976.9</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.0142</v>
+        <v>0.1254</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>68.98</v>
+        <v>7.79</v>
       </c>
       <c r="I22" s="5" t="inlineStr"/>
     </row>
@@ -9089,13 +9044,13 @@
         </is>
       </c>
       <c r="F23" s="6" t="n">
-        <v>13498.8</v>
+        <v>331.5</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.0741</v>
+        <v>3.0168</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>843.67</v>
+        <v>20.72</v>
       </c>
       <c r="I23" s="5" t="inlineStr"/>
     </row>
@@ -9124,13 +9079,13 @@
         </is>
       </c>
       <c r="F24" s="6" t="n">
-        <v>75945.60000000001</v>
+        <v>11979.3</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.0132</v>
+        <v>0.0835</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>4.64</v>
+        <v>0.73</v>
       </c>
       <c r="I24" s="5" t="inlineStr"/>
     </row>
@@ -9159,13 +9114,13 @@
         </is>
       </c>
       <c r="F25" s="6" t="n">
-        <v>69146.10000000001</v>
+        <v>7884.1</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.0145</v>
+        <v>0.1268</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>67.53</v>
+        <v>7.7</v>
       </c>
       <c r="I25" s="5" t="inlineStr"/>
     </row>
@@ -9194,13 +9149,13 @@
         </is>
       </c>
       <c r="F26" s="6" t="n">
-        <v>10655.9</v>
+        <v>329</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.09379999999999999</v>
+        <v>3.0396</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>666</v>
+        <v>20.56</v>
       </c>
       <c r="I26" s="5" t="inlineStr"/>
     </row>
@@ -9229,13 +9184,13 @@
         </is>
       </c>
       <c r="F27" s="6" t="n">
-        <v>62435.2</v>
+        <v>10358.4</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.016</v>
+        <v>0.0965</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>3.81</v>
+        <v>0.63</v>
       </c>
       <c r="I27" s="5" t="inlineStr"/>
     </row>
@@ -9264,13 +9219,13 @@
         </is>
       </c>
       <c r="F28" s="6" t="n">
-        <v>58775.8</v>
+        <v>5526.6</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.017</v>
+        <v>0.1809</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>57.4</v>
+        <v>5.4</v>
       </c>
       <c r="I28" s="5" t="inlineStr"/>
     </row>
@@ -9299,13 +9254,13 @@
         </is>
       </c>
       <c r="F29" s="6" t="n">
-        <v>16576.5</v>
+        <v>172.9</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.0603</v>
+        <v>5.7824</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>1036.03</v>
+        <v>10.81</v>
       </c>
       <c r="I29" s="5" t="inlineStr"/>
     </row>
@@ -9334,13 +9289,13 @@
         </is>
       </c>
       <c r="F30" s="6" t="n">
-        <v>430.4</v>
+        <v>10.5</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>2.3235</v>
+        <v>95.0163</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>430.38</v>
+        <v>10.52</v>
       </c>
       <c r="I30" s="5" t="inlineStr"/>
     </row>
@@ -9369,13 +9324,13 @@
         </is>
       </c>
       <c r="F31" s="6" t="n">
-        <v>57906.1</v>
+        <v>10230</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.0173</v>
+        <v>0.0978</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>3.53</v>
+        <v>0.62</v>
       </c>
       <c r="I31" s="5" t="inlineStr"/>
     </row>
@@ -9404,13 +9359,13 @@
         </is>
       </c>
       <c r="F32" s="6" t="n">
-        <v>59373.9</v>
+        <v>5427.1</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.0168</v>
+        <v>0.1843</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>57.98</v>
+        <v>5.3</v>
       </c>
       <c r="I32" s="5" t="inlineStr"/>
     </row>
@@ -9439,13 +9394,13 @@
         </is>
       </c>
       <c r="F33" s="6" t="n">
-        <v>15144</v>
+        <v>169.4</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0.066</v>
+        <v>5.9016</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>946.5</v>
+        <v>10.59</v>
       </c>
       <c r="I33" s="5" t="inlineStr"/>
     </row>
@@ -9474,13 +9429,13 @@
         </is>
       </c>
       <c r="F34" s="6" t="n">
-        <v>434.9</v>
+        <v>10.5</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>2.2992</v>
+        <v>95.25839999999999</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>434.94</v>
+        <v>10.5</v>
       </c>
       <c r="I34" s="5" t="inlineStr"/>
     </row>
@@ -9509,13 +9464,13 @@
         </is>
       </c>
       <c r="F35" s="6" t="n">
-        <v>60906.3</v>
+        <v>4425.7</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>0.0164</v>
+        <v>0.226</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>59.48</v>
+        <v>4.32</v>
       </c>
       <c r="I35" s="5" t="inlineStr"/>
     </row>
@@ -9544,13 +9499,13 @@
         </is>
       </c>
       <c r="F36" s="6" t="n">
-        <v>10797.1</v>
+        <v>117.8</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>0.0926</v>
+        <v>8.4878</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>674.8200000000001</v>
+        <v>7.36</v>
       </c>
       <c r="I36" s="5" t="inlineStr"/>
     </row>
@@ -9579,13 +9534,13 @@
         </is>
       </c>
       <c r="F37" s="6" t="n">
-        <v>61497.1</v>
+        <v>4407</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>0.0163</v>
+        <v>0.2269</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>60.06</v>
+        <v>4.3</v>
       </c>
       <c r="I37" s="5" t="inlineStr"/>
     </row>
@@ -9614,13 +9569,13 @@
         </is>
       </c>
       <c r="F38" s="6" t="n">
-        <v>11004.5</v>
+        <v>119.2</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>0.09089999999999999</v>
+        <v>8.3901</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>687.78</v>
+        <v>7.45</v>
       </c>
       <c r="I38" s="5" t="inlineStr"/>
     </row>
@@ -9649,13 +9604,13 @@
         </is>
       </c>
       <c r="F39" s="6" t="n">
-        <v>61154</v>
+        <v>7604</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>0.0164</v>
+        <v>0.1315</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>59.72</v>
+        <v>7.43</v>
       </c>
       <c r="I39" s="5" t="inlineStr"/>
     </row>
@@ -9684,13 +9639,13 @@
         </is>
       </c>
       <c r="F40" s="6" t="n">
-        <v>27449.5</v>
+        <v>325.3</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>0.0364</v>
+        <v>3.0743</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>1715.59</v>
+        <v>20.33</v>
       </c>
       <c r="I40" s="5" t="inlineStr"/>
     </row>
@@ -9719,13 +9674,13 @@
         </is>
       </c>
       <c r="F41" s="6" t="n">
-        <v>59056.1</v>
+        <v>7250.8</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>0.0169</v>
+        <v>0.1379</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>57.67</v>
+        <v>7.08</v>
       </c>
       <c r="I41" s="5" t="inlineStr"/>
     </row>
@@ -9754,13 +9709,13 @@
         </is>
       </c>
       <c r="F42" s="6" t="n">
-        <v>25435.2</v>
+        <v>327.9</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>0.0393</v>
+        <v>3.0497</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>1589.7</v>
+        <v>20.49</v>
       </c>
       <c r="I42" s="5" t="inlineStr"/>
     </row>
@@ -9783,7 +9738,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>72979.8</v>
+        <v>10815.6</v>
       </c>
     </row>
     <row r="47">
@@ -9793,7 +9748,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>66503</v>
+        <v>5566.3</v>
       </c>
     </row>
     <row r="48">
@@ -9803,7 +9758,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>9831.799999999999</v>
+        <v>167.1</v>
       </c>
     </row>
     <row r="49">
@@ -9813,7 +9768,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>336.1</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="50">
@@ -9823,7 +9778,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>65721.8</v>
+        <v>5396.6</v>
       </c>
     </row>
     <row r="51">
@@ -9833,7 +9788,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>9036.700000000001</v>
+        <v>169.7</v>
       </c>
     </row>
     <row r="52">
@@ -9843,7 +9798,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>73947.89999999999</v>
+        <v>11064.9</v>
       </c>
     </row>
     <row r="53">
@@ -9853,7 +9808,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>65620.60000000001</v>
+        <v>5628</v>
       </c>
     </row>
     <row r="54">
@@ -9863,7 +9818,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>8414.6</v>
+        <v>168.7</v>
       </c>
     </row>
     <row r="55">
@@ -9873,7 +9828,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>307.7</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="56">
@@ -9883,7 +9838,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>76377.89999999999</v>
+        <v>11150.1</v>
       </c>
     </row>
     <row r="57">
@@ -9893,7 +9848,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>67089.10000000001</v>
+        <v>5031.1</v>
       </c>
     </row>
     <row r="58">
@@ -9903,7 +9858,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>10771.7</v>
+        <v>143.1</v>
       </c>
     </row>
     <row r="59">
@@ -9913,7 +9868,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>374</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="60">
@@ -9923,7 +9878,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>76018.8</v>
+        <v>10438</v>
       </c>
     </row>
     <row r="61">
@@ -9933,7 +9888,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>64676.3</v>
+        <v>4876.7</v>
       </c>
     </row>
     <row r="62">
@@ -9943,7 +9898,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>10895.3</v>
+        <v>140.3</v>
       </c>
     </row>
     <row r="63">
@@ -9953,7 +9908,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>371.5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="64">
@@ -9963,7 +9918,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>76104.60000000001</v>
+        <v>12372.7</v>
       </c>
     </row>
     <row r="65">
@@ -9973,7 +9928,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>70636.7</v>
+        <v>7976.9</v>
       </c>
     </row>
     <row r="66">
@@ -9983,7 +9938,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>13498.8</v>
+        <v>331.5</v>
       </c>
     </row>
     <row r="67">
@@ -9993,7 +9948,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>75945.60000000001</v>
+        <v>11979.3</v>
       </c>
     </row>
     <row r="68">
@@ -10003,7 +9958,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>69146.10000000001</v>
+        <v>7884.1</v>
       </c>
     </row>
     <row r="69">
@@ -10013,7 +9968,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>10655.9</v>
+        <v>329</v>
       </c>
     </row>
     <row r="70">
@@ -10023,7 +9978,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>62435.2</v>
+        <v>10358.4</v>
       </c>
     </row>
     <row r="71">
@@ -10033,7 +9988,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>58775.8</v>
+        <v>5526.6</v>
       </c>
     </row>
     <row r="72">
@@ -10043,7 +9998,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>16576.5</v>
+        <v>172.9</v>
       </c>
     </row>
     <row r="73">
@@ -10053,7 +10008,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>430.4</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="74">
@@ -10063,7 +10018,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>57906.1</v>
+        <v>10230</v>
       </c>
     </row>
     <row r="75">
@@ -10073,7 +10028,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>59373.9</v>
+        <v>5427.1</v>
       </c>
     </row>
     <row r="76">
@@ -10083,7 +10038,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>15144</v>
+        <v>169.4</v>
       </c>
     </row>
     <row r="77">
@@ -10093,7 +10048,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>434.9</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="78">
@@ -10103,7 +10058,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>60906.3</v>
+        <v>4425.7</v>
       </c>
     </row>
     <row r="79">
@@ -10113,7 +10068,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>10797.1</v>
+        <v>117.8</v>
       </c>
     </row>
     <row r="80">
@@ -10123,7 +10078,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>61497.1</v>
+        <v>4407</v>
       </c>
     </row>
     <row r="81">
@@ -10133,7 +10088,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>11004.5</v>
+        <v>119.2</v>
       </c>
     </row>
     <row r="82">
@@ -10143,7 +10098,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>61154</v>
+        <v>7604</v>
       </c>
     </row>
     <row r="83">
@@ -10153,7 +10108,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>27449.5</v>
+        <v>325.3</v>
       </c>
     </row>
     <row r="84">
@@ -10163,7 +10118,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>59056.1</v>
+        <v>7250.8</v>
       </c>
     </row>
     <row r="85">
@@ -10173,7 +10128,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>25435.2</v>
+        <v>327.9</v>
       </c>
     </row>
   </sheetData>
@@ -10285,13 +10240,13 @@
         </is>
       </c>
       <c r="F3" s="9" t="n">
-        <v>61158.9</v>
+        <v>11192.5</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>0.0164</v>
+        <v>0.0893</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>3.73</v>
+        <v>0.68</v>
       </c>
       <c r="I3" s="8" t="inlineStr"/>
     </row>
@@ -10320,13 +10275,13 @@
         </is>
       </c>
       <c r="F4" s="9" t="n">
-        <v>17658.7</v>
+        <v>4434</v>
       </c>
       <c r="G4" s="9" t="n">
-        <v>0.0566</v>
+        <v>0.2255</v>
       </c>
       <c r="H4" s="9" t="n">
-        <v>17.24</v>
+        <v>4.33</v>
       </c>
       <c r="I4" s="8" t="inlineStr"/>
     </row>
@@ -10355,13 +10310,13 @@
         </is>
       </c>
       <c r="F5" s="9" t="n">
-        <v>360.5</v>
+        <v>120.9</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>2.7736</v>
+        <v>8.2723</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>22.53</v>
+        <v>7.56</v>
       </c>
       <c r="I5" s="8" t="inlineStr"/>
     </row>
@@ -10390,13 +10345,13 @@
         </is>
       </c>
       <c r="F6" s="9" t="n">
-        <v>60446.2</v>
+        <v>11805.6</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>0.0165</v>
+        <v>0.0847</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>3.69</v>
+        <v>0.72</v>
       </c>
       <c r="I6" s="8" t="inlineStr"/>
     </row>
@@ -10425,13 +10380,13 @@
         </is>
       </c>
       <c r="F7" s="9" t="n">
-        <v>18328.2</v>
+        <v>6086.7</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>0.0546</v>
+        <v>0.1643</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>17.9</v>
+        <v>5.94</v>
       </c>
       <c r="I7" s="8" t="inlineStr"/>
     </row>
@@ -10460,13 +10415,13 @@
         </is>
       </c>
       <c r="F8" s="9" t="n">
-        <v>393.1</v>
+        <v>185.4</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>2.5439</v>
+        <v>5.395</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>24.57</v>
+        <v>11.58</v>
       </c>
       <c r="I8" s="8" t="inlineStr"/>
     </row>
@@ -10489,7 +10444,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>61158.9</v>
+        <v>11192.5</v>
       </c>
     </row>
     <row r="13">
@@ -10499,7 +10454,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17658.7</v>
+        <v>4434</v>
       </c>
     </row>
     <row r="14">
@@ -10509,7 +10464,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>360.5</v>
+        <v>120.9</v>
       </c>
     </row>
     <row r="15">
@@ -10519,7 +10474,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>60446.2</v>
+        <v>11805.6</v>
       </c>
     </row>
     <row r="16">
@@ -10529,7 +10484,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18328.2</v>
+        <v>6086.7</v>
       </c>
     </row>
     <row r="17">
@@ -10539,7 +10494,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>393.1</v>
+        <v>185.4</v>
       </c>
     </row>
   </sheetData>
@@ -10558,7 +10513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10651,10 +10606,10 @@
         </is>
       </c>
       <c r="F3" s="12" t="n">
-        <v>3425.7</v>
+        <v>1320.8</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>0.2919</v>
+        <v>0.7571</v>
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
@@ -10688,10 +10643,10 @@
         </is>
       </c>
       <c r="F4" s="12" t="n">
-        <v>1270.3</v>
+        <v>578</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>0.7872</v>
+        <v>1.7301</v>
       </c>
       <c r="H4" s="12" t="inlineStr">
         <is>
@@ -10725,10 +10680,10 @@
         </is>
       </c>
       <c r="F5" s="12" t="n">
-        <v>576.9</v>
+        <v>282</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>1.7333</v>
+        <v>3.5456</v>
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
@@ -10762,10 +10717,10 @@
         </is>
       </c>
       <c r="F6" s="12" t="n">
-        <v>297.5</v>
+        <v>152.8</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>3.3611</v>
+        <v>6.5466</v>
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
@@ -10799,10 +10754,10 @@
         </is>
       </c>
       <c r="F7" s="12" t="n">
-        <v>46211.3</v>
+        <v>8377</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.0216</v>
+        <v>0.1194</v>
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
@@ -10836,10 +10791,10 @@
         </is>
       </c>
       <c r="F8" s="12" t="n">
-        <v>25380.5</v>
+        <v>7262.4</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.0394</v>
+        <v>0.1377</v>
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
@@ -10873,10 +10828,10 @@
         </is>
       </c>
       <c r="F9" s="12" t="n">
-        <v>15042.3</v>
+        <v>5040.9</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.0665</v>
+        <v>0.1984</v>
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
@@ -10910,10 +10865,10 @@
         </is>
       </c>
       <c r="F10" s="12" t="n">
-        <v>9720.9</v>
+        <v>4228.7</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.1029</v>
+        <v>0.2365</v>
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
@@ -10947,13 +10902,13 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>26587.2</v>
+        <v>8962.4</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.0376</v>
+        <v>0.1116</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>1.62</v>
+        <v>0.55</v>
       </c>
       <c r="I11" s="11" t="inlineStr"/>
     </row>
@@ -10982,13 +10937,13 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>1205.2</v>
+        <v>583.4</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.8297</v>
+        <v>1.714</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="I12" s="11" t="inlineStr"/>
     </row>
@@ -11017,10 +10972,10 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>1223.9</v>
+        <v>587.3</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.8169999999999999</v>
+        <v>1.7028</v>
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
@@ -11054,10 +11009,10 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>1151.5</v>
+        <v>571.2</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.8683999999999999</v>
+        <v>1.7506</v>
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
@@ -11091,10 +11046,10 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>1233</v>
+        <v>575.3</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.8110000000000001</v>
+        <v>1.7382</v>
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
@@ -11128,10 +11083,10 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>19851.1</v>
+        <v>6707.5</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.0504</v>
+        <v>0.1491</v>
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
@@ -11165,10 +11120,10 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>22922.8</v>
+        <v>6605.3</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.0436</v>
+        <v>0.1514</v>
       </c>
       <c r="H17" s="12" t="inlineStr">
         <is>
@@ -11190,7 +11145,7 @@
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>encrypt</t>
+          <t>decrypt</t>
         </is>
       </c>
       <c r="D18" s="11" t="n">
@@ -11202,61 +11157,36 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>25554</v>
+        <v>587</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.0391</v>
+        <v>1.7037</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>6.24</v>
+        <v>0.14</v>
       </c>
       <c r="I18" s="11" t="inlineStr"/>
     </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>RSA</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>RSA_X_509</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>decrypt</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="n">
-        <v>2048</v>
-      </c>
-      <c r="E19" s="11" t="inlineStr">
-        <is>
-          <t>256 B</t>
-        </is>
-      </c>
-      <c r="F19" s="12" t="n">
-        <v>1196.6</v>
-      </c>
-      <c r="G19" s="12" t="n">
-        <v>0.8357</v>
-      </c>
-      <c r="H19" s="12" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="I19" s="11" t="inlineStr"/>
+    <row r="21">
+      <c r="A21" s="38" t="inlineStr">
+        <is>
+          <t>Opération</t>
+        </is>
+      </c>
+      <c r="B21" s="38" t="inlineStr">
+        <is>
+          <t>Ops/s</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="38" t="inlineStr">
-        <is>
-          <t>Opération</t>
-        </is>
-      </c>
-      <c r="B22" s="38" t="inlineStr">
-        <is>
-          <t>Ops/s</t>
-        </is>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SHA256_RSA_PKCS sign</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1320.8</v>
       </c>
     </row>
     <row r="23">
@@ -11266,7 +11196,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3425.7</v>
+        <v>578</v>
       </c>
     </row>
     <row r="24">
@@ -11276,7 +11206,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1270.3</v>
+        <v>282</v>
       </c>
     </row>
     <row r="25">
@@ -11286,17 +11216,17 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>576.9</v>
+        <v>152.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SHA256_RSA_PKCS sign</t>
+          <t>SHA256_RSA_PKCS verify</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>297.5</v>
+        <v>8377</v>
       </c>
     </row>
     <row r="27">
@@ -11306,7 +11236,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>46211.3</v>
+        <v>7262.4</v>
       </c>
     </row>
     <row r="28">
@@ -11316,7 +11246,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>25380.5</v>
+        <v>5040.9</v>
       </c>
     </row>
     <row r="29">
@@ -11326,111 +11256,91 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>15042.3</v>
+        <v>4228.7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SHA256_RSA_PKCS verify</t>
+          <t>RSA_PKCS_OAEP encrypt 64 B</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>9720.9</v>
+        <v>8962.4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>RSA_PKCS_OAEP encrypt 64 B</t>
+          <t>RSA_PKCS_OAEP decrypt 64 B</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>26587.2</v>
+        <v>583.4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>RSA_PKCS_OAEP decrypt 64 B</t>
+          <t>RSA_PKCS_PSS_SHA1 sign</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1205.2</v>
+        <v>587.3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>RSA_PKCS_PSS_SHA1 sign</t>
+          <t>RSA_PKCS_PSS_SHA256 sign</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1223.9</v>
+        <v>571.2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>RSA_PKCS_PSS_SHA256 sign</t>
+          <t>RSA_PKCS_PSS_SHA512 sign</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1151.5</v>
+        <v>575.3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RSA_PKCS_PSS_SHA512 sign</t>
+          <t>RSA_PKCS_PSS_SHA256 verify</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1233</v>
+        <v>6707.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>RSA_PKCS_PSS_SHA256 verify</t>
+          <t>RSA_PKCS_PSS_SHA512 verify</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>19851.1</v>
+        <v>6605.3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>RSA_PKCS_PSS_SHA512 verify</t>
+          <t>RSA_X_509 decrypt 256 B</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>22922.8</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>RSA_X_509 encrypt 256 B</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>25554</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>RSA_X_509 decrypt 256 B</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>1196.6</v>
+        <v>587</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:I19"/>
+  <autoFilter ref="A2:I18"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -11538,10 +11448,10 @@
         </is>
       </c>
       <c r="F3" s="15" t="n">
-        <v>15954</v>
+        <v>5524</v>
       </c>
       <c r="G3" s="15" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.181</v>
       </c>
       <c r="H3" s="15" t="inlineStr">
         <is>
@@ -11575,10 +11485,10 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>1173.4</v>
+        <v>810.6</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>0.8522</v>
+        <v>1.2336</v>
       </c>
       <c r="H4" s="15" t="inlineStr">
         <is>
@@ -11612,10 +11522,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>3073.8</v>
+        <v>1820.3</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0.3253</v>
+        <v>0.5494</v>
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
@@ -11649,10 +11559,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>9280.299999999999</v>
+        <v>5522.2</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0.1078</v>
+        <v>0.1811</v>
       </c>
       <c r="H6" s="15" t="inlineStr">
         <is>
@@ -11686,10 +11596,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>1381.1</v>
+        <v>980.1</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0.7241</v>
+        <v>1.0203</v>
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
@@ -11723,10 +11633,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n">
-        <v>1705.7</v>
+        <v>1295.9</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0.5863</v>
+        <v>0.7716</v>
       </c>
       <c r="H8" s="15" t="inlineStr">
         <is>
@@ -11760,10 +11670,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>4148.2</v>
+        <v>1228.9</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0.2411</v>
+        <v>0.8137</v>
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
@@ -11797,10 +11707,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>1063.6</v>
+        <v>568.8</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0.9402</v>
+        <v>1.7582</v>
       </c>
       <c r="H10" s="15" t="inlineStr">
         <is>
@@ -11834,10 +11744,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>1886.5</v>
+        <v>812.2</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0.5301</v>
+        <v>1.2312</v>
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
@@ -11865,7 +11775,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15954</v>
+        <v>5524</v>
       </c>
     </row>
     <row r="16">
@@ -11875,7 +11785,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1173.4</v>
+        <v>810.6</v>
       </c>
     </row>
     <row r="17">
@@ -11885,7 +11795,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3073.8</v>
+        <v>1820.3</v>
       </c>
     </row>
     <row r="18">
@@ -11895,7 +11805,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>9280.299999999999</v>
+        <v>5522.2</v>
       </c>
     </row>
     <row r="19">
@@ -11905,7 +11815,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1381.1</v>
+        <v>980.1</v>
       </c>
     </row>
     <row r="20">
@@ -11915,7 +11825,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1705.7</v>
+        <v>1295.9</v>
       </c>
     </row>
     <row r="21">
@@ -11925,7 +11835,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4148.2</v>
+        <v>1228.9</v>
       </c>
     </row>
     <row r="22">
@@ -11935,7 +11845,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1063.6</v>
+        <v>568.8</v>
       </c>
     </row>
     <row r="23">
@@ -11945,7 +11855,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1886.5</v>
+        <v>812.2</v>
       </c>
     </row>
   </sheetData>
@@ -12057,13 +11967,13 @@
         </is>
       </c>
       <c r="F3" s="18" t="n">
-        <v>4347.3</v>
+        <v>2555.7</v>
       </c>
       <c r="G3" s="18" t="n">
-        <v>0.23</v>
+        <v>0.3913</v>
       </c>
       <c r="H3" s="18" t="n">
-        <v>0.27</v>
+        <v>0.16</v>
       </c>
       <c r="I3" s="17" t="inlineStr"/>
     </row>
@@ -12092,13 +12002,13 @@
         </is>
       </c>
       <c r="F4" s="18" t="n">
-        <v>4940.8</v>
+        <v>2361.4</v>
       </c>
       <c r="G4" s="18" t="n">
-        <v>0.2024</v>
+        <v>0.4235</v>
       </c>
       <c r="H4" s="18" t="n">
-        <v>4.83</v>
+        <v>2.31</v>
       </c>
       <c r="I4" s="17" t="inlineStr"/>
     </row>
@@ -12127,13 +12037,13 @@
         </is>
       </c>
       <c r="F5" s="18" t="n">
-        <v>4493.7</v>
+        <v>2933.2</v>
       </c>
       <c r="G5" s="18" t="n">
-        <v>0.2225</v>
+        <v>0.3409</v>
       </c>
       <c r="H5" s="18" t="n">
-        <v>0.27</v>
+        <v>0.18</v>
       </c>
       <c r="I5" s="17" t="inlineStr"/>
     </row>
@@ -12162,13 +12072,13 @@
         </is>
       </c>
       <c r="F6" s="18" t="n">
-        <v>4622.1</v>
+        <v>2586.7</v>
       </c>
       <c r="G6" s="18" t="n">
-        <v>0.2164</v>
+        <v>0.3866</v>
       </c>
       <c r="H6" s="18" t="n">
-        <v>4.51</v>
+        <v>2.53</v>
       </c>
       <c r="I6" s="17" t="inlineStr"/>
     </row>
@@ -12191,7 +12101,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4347.3</v>
+        <v>2555.7</v>
       </c>
     </row>
     <row r="11">
@@ -12201,7 +12111,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4940.8</v>
+        <v>2361.4</v>
       </c>
     </row>
     <row r="12">
@@ -12211,7 +12121,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4493.7</v>
+        <v>2933.2</v>
       </c>
     </row>
     <row r="13">
@@ -12221,7 +12131,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4622.1</v>
+        <v>2586.7</v>
       </c>
     </row>
   </sheetData>
@@ -12333,10 +12243,10 @@
         </is>
       </c>
       <c r="F3" s="21" t="n">
-        <v>4703.5</v>
+        <v>2340</v>
       </c>
       <c r="G3" s="21" t="n">
-        <v>0.2126</v>
+        <v>0.4274</v>
       </c>
       <c r="H3" s="21" t="inlineStr">
         <is>
@@ -12370,10 +12280,10 @@
         </is>
       </c>
       <c r="F4" s="21" t="n">
-        <v>10344</v>
+        <v>4712.6</v>
       </c>
       <c r="G4" s="21" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.2122</v>
       </c>
       <c r="H4" s="21" t="inlineStr">
         <is>
@@ -12401,7 +12311,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4703.5</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="9">
@@ -12411,7 +12321,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10344</v>
+        <v>4712.6</v>
       </c>
     </row>
   </sheetData>
@@ -12523,10 +12433,10 @@
         </is>
       </c>
       <c r="F3" s="24" t="n">
-        <v>4364.6</v>
+        <v>1174.8</v>
       </c>
       <c r="G3" s="24" t="n">
-        <v>0.2291</v>
+        <v>0.8512</v>
       </c>
       <c r="H3" s="24" t="inlineStr">
         <is>
@@ -12554,7 +12464,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4364.6</v>
+        <v>1174.8</v>
       </c>
     </row>
   </sheetData>
@@ -12666,13 +12576,13 @@
         </is>
       </c>
       <c r="F3" s="27" t="n">
-        <v>62986.4</v>
+        <v>9570</v>
       </c>
       <c r="G3" s="27" t="n">
-        <v>0.0159</v>
+        <v>0.1045</v>
       </c>
       <c r="H3" s="27" t="n">
-        <v>3.84</v>
+        <v>0.58</v>
       </c>
       <c r="I3" s="26" t="inlineStr"/>
     </row>
@@ -12701,13 +12611,13 @@
         </is>
       </c>
       <c r="F4" s="27" t="n">
-        <v>67043.8</v>
+        <v>5641.3</v>
       </c>
       <c r="G4" s="27" t="n">
-        <v>0.0149</v>
+        <v>0.1773</v>
       </c>
       <c r="H4" s="27" t="n">
-        <v>65.47</v>
+        <v>5.51</v>
       </c>
       <c r="I4" s="26" t="inlineStr"/>
     </row>
@@ -12736,13 +12646,13 @@
         </is>
       </c>
       <c r="F5" s="27" t="n">
-        <v>15148.2</v>
+        <v>591.4</v>
       </c>
       <c r="G5" s="27" t="n">
-        <v>0.066</v>
+        <v>1.6908</v>
       </c>
       <c r="H5" s="27" t="n">
-        <v>946.76</v>
+        <v>36.96</v>
       </c>
       <c r="I5" s="26" t="inlineStr"/>
     </row>
@@ -12771,13 +12681,13 @@
         </is>
       </c>
       <c r="F6" s="27" t="n">
-        <v>70750.7</v>
+        <v>12473.1</v>
       </c>
       <c r="G6" s="27" t="n">
-        <v>0.0141</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="H6" s="27" t="n">
-        <v>4.32</v>
+        <v>0.76</v>
       </c>
       <c r="I6" s="26" t="inlineStr"/>
     </row>
@@ -12806,13 +12716,13 @@
         </is>
       </c>
       <c r="F7" s="27" t="n">
-        <v>60716.5</v>
+        <v>9561.6</v>
       </c>
       <c r="G7" s="27" t="n">
-        <v>0.0165</v>
+        <v>0.1046</v>
       </c>
       <c r="H7" s="27" t="n">
-        <v>59.29</v>
+        <v>9.34</v>
       </c>
       <c r="I7" s="26" t="inlineStr"/>
     </row>
@@ -12841,13 +12751,13 @@
         </is>
       </c>
       <c r="F8" s="27" t="n">
-        <v>14234.6</v>
+        <v>574.6</v>
       </c>
       <c r="G8" s="27" t="n">
-        <v>0.0703</v>
+        <v>1.7403</v>
       </c>
       <c r="H8" s="27" t="n">
-        <v>889.66</v>
+        <v>35.91</v>
       </c>
       <c r="I8" s="26" t="inlineStr"/>
     </row>
@@ -12876,13 +12786,13 @@
         </is>
       </c>
       <c r="F9" s="27" t="n">
-        <v>1088.4</v>
+        <v>37.9</v>
       </c>
       <c r="G9" s="27" t="n">
-        <v>0.9188</v>
+        <v>26.409</v>
       </c>
       <c r="H9" s="27" t="n">
-        <v>1088.43</v>
+        <v>37.87</v>
       </c>
       <c r="I9" s="26" t="inlineStr"/>
     </row>
@@ -12911,13 +12821,13 @@
         </is>
       </c>
       <c r="F10" s="27" t="n">
-        <v>7466.8</v>
+        <v>587.1</v>
       </c>
       <c r="G10" s="27" t="n">
-        <v>0.1339</v>
+        <v>1.7033</v>
       </c>
       <c r="H10" s="27" t="n">
-        <v>466.68</v>
+        <v>36.69</v>
       </c>
       <c r="I10" s="26" t="inlineStr"/>
     </row>
@@ -12946,13 +12856,13 @@
         </is>
       </c>
       <c r="F11" s="27" t="n">
-        <v>7585.3</v>
+        <v>584.1</v>
       </c>
       <c r="G11" s="27" t="n">
-        <v>0.1318</v>
+        <v>1.7121</v>
       </c>
       <c r="H11" s="27" t="n">
-        <v>474.08</v>
+        <v>36.51</v>
       </c>
       <c r="I11" s="26" t="inlineStr"/>
     </row>
@@ -12981,13 +12891,13 @@
         </is>
       </c>
       <c r="F12" s="27" t="n">
-        <v>521.1</v>
+        <v>38.8</v>
       </c>
       <c r="G12" s="27" t="n">
-        <v>1.919</v>
+        <v>25.8014</v>
       </c>
       <c r="H12" s="27" t="n">
-        <v>521.11</v>
+        <v>38.76</v>
       </c>
       <c r="I12" s="26" t="inlineStr"/>
     </row>
@@ -13016,13 +12926,13 @@
         </is>
       </c>
       <c r="F13" s="27" t="n">
-        <v>72528.5</v>
+        <v>13091.1</v>
       </c>
       <c r="G13" s="27" t="n">
-        <v>0.0138</v>
+        <v>0.0764</v>
       </c>
       <c r="H13" s="27" t="n">
-        <v>4.43</v>
+        <v>0.8</v>
       </c>
       <c r="I13" s="26" t="inlineStr"/>
     </row>
@@ -13051,13 +12961,13 @@
         </is>
       </c>
       <c r="F14" s="27" t="n">
-        <v>66169</v>
+        <v>9997.799999999999</v>
       </c>
       <c r="G14" s="27" t="n">
-        <v>0.0151</v>
+        <v>0.1</v>
       </c>
       <c r="H14" s="27" t="n">
-        <v>64.62</v>
+        <v>9.76</v>
       </c>
       <c r="I14" s="26" t="inlineStr"/>
     </row>
@@ -13086,13 +12996,13 @@
         </is>
       </c>
       <c r="F15" s="27" t="n">
-        <v>9931.200000000001</v>
+        <v>609.2</v>
       </c>
       <c r="G15" s="27" t="n">
-        <v>0.1007</v>
+        <v>1.6415</v>
       </c>
       <c r="H15" s="27" t="n">
-        <v>620.7</v>
+        <v>38.07</v>
       </c>
       <c r="I15" s="26" t="inlineStr"/>
     </row>
@@ -13121,13 +13031,13 @@
         </is>
       </c>
       <c r="F16" s="27" t="n">
-        <v>55220.3</v>
+        <v>12715.4</v>
       </c>
       <c r="G16" s="27" t="n">
-        <v>0.0181</v>
+        <v>0.0786</v>
       </c>
       <c r="H16" s="27" t="n">
-        <v>3.37</v>
+        <v>0.78</v>
       </c>
       <c r="I16" s="26" t="inlineStr"/>
     </row>
@@ -13156,13 +13066,13 @@
         </is>
       </c>
       <c r="F17" s="27" t="n">
-        <v>16280.2</v>
+        <v>6851.2</v>
       </c>
       <c r="G17" s="27" t="n">
-        <v>0.0614</v>
+        <v>0.146</v>
       </c>
       <c r="H17" s="27" t="n">
-        <v>15.9</v>
+        <v>6.69</v>
       </c>
       <c r="I17" s="26" t="inlineStr"/>
     </row>
@@ -13191,13 +13101,13 @@
         </is>
       </c>
       <c r="F18" s="27" t="n">
-        <v>347.8</v>
+        <v>235</v>
       </c>
       <c r="G18" s="27" t="n">
-        <v>2.8754</v>
+        <v>4.2549</v>
       </c>
       <c r="H18" s="27" t="n">
-        <v>21.74</v>
+        <v>14.69</v>
       </c>
       <c r="I18" s="26" t="inlineStr"/>
     </row>
@@ -13220,7 +13130,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>62986.4</v>
+        <v>9570</v>
       </c>
     </row>
     <row r="23">
@@ -13230,7 +13140,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>67043.8</v>
+        <v>5641.3</v>
       </c>
     </row>
     <row r="24">
@@ -13240,7 +13150,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>15148.2</v>
+        <v>591.4</v>
       </c>
     </row>
     <row r="25">
@@ -13250,7 +13160,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>70750.7</v>
+        <v>12473.1</v>
       </c>
     </row>
     <row r="26">
@@ -13260,7 +13170,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>60716.5</v>
+        <v>9561.6</v>
       </c>
     </row>
     <row r="27">
@@ -13270,7 +13180,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>14234.6</v>
+        <v>574.6</v>
       </c>
     </row>
     <row r="28">
@@ -13280,7 +13190,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1088.4</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="29">
@@ -13290,7 +13200,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>7466.8</v>
+        <v>587.1</v>
       </c>
     </row>
     <row r="30">
@@ -13300,7 +13210,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>7585.3</v>
+        <v>584.1</v>
       </c>
     </row>
     <row r="31">
@@ -13310,7 +13220,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>521.1</v>
+        <v>38.8</v>
       </c>
     </row>
     <row r="32">
@@ -13320,7 +13230,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>72528.5</v>
+        <v>13091.1</v>
       </c>
     </row>
     <row r="33">
@@ -13330,7 +13240,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>66169</v>
+        <v>9997.799999999999</v>
       </c>
     </row>
     <row r="34">
@@ -13340,7 +13250,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>9931.200000000001</v>
+        <v>609.2</v>
       </c>
     </row>
     <row r="35">
@@ -13350,7 +13260,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>55220.3</v>
+        <v>12715.4</v>
       </c>
     </row>
     <row r="36">
@@ -13360,7 +13270,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>16280.2</v>
+        <v>6851.2</v>
       </c>
     </row>
     <row r="37">
@@ -13370,7 +13280,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>347.8</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
